--- a/research/traditional_assets/database/data/romania/romania_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_real_estate_operations_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvb_mece" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.153</v>
+        <v>0.145</v>
       </c>
       <c r="G2">
-        <v>-0.902676399026764</v>
+        <v>0.1547332185886403</v>
       </c>
       <c r="H2">
-        <v>-0.902676399026764</v>
+        <v>0.1547332185886403</v>
       </c>
       <c r="I2">
-        <v>-0.5790754257907542</v>
+        <v>-0.05490533562822718</v>
       </c>
       <c r="J2">
-        <v>-0.5790754257907542</v>
+        <v>-0.05291280328688023</v>
       </c>
       <c r="K2">
-        <v>-0.229</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="L2">
-        <v>-0.5571776155717763</v>
+        <v>-0.03442340791738385</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.001102756892230576</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.2199999999999998</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,70 +629,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.044</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.141</v>
+        <v>1.091</v>
       </c>
       <c r="V2">
-        <v>0.01305555555555555</v>
+        <v>0.02734335839598998</v>
       </c>
       <c r="W2">
-        <v>-0.01186528497409326</v>
+        <v>-0.02102949723917466</v>
       </c>
       <c r="X2">
-        <v>0.05379899011795157</v>
+        <v>0.09540703757674449</v>
       </c>
       <c r="Y2">
-        <v>-0.06566427509204484</v>
+        <v>-0.1164365348159191</v>
       </c>
       <c r="Z2">
-        <v>0.02162019989479221</v>
+        <v>0.0980541069650482</v>
       </c>
       <c r="AA2">
-        <v>-0.01251972645975802</v>
+        <v>-0.02285054081149846</v>
       </c>
       <c r="AB2">
-        <v>0.05379899011795157</v>
+        <v>0.09391274297951935</v>
       </c>
       <c r="AC2">
-        <v>-0.06631871657770959</v>
+        <v>-0.1167632837910178</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AG2">
-        <v>-0.141</v>
+        <v>1.759</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.05682951146560319</v>
       </c>
       <c r="AJ2">
-        <v>-0.01322825781030115</v>
+        <v>0.04222376917352794</v>
       </c>
       <c r="AK2">
-        <v>-0.007680156871289284</v>
+        <v>0.035854787093092</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>4.930795847750865</v>
+      </c>
+      <c r="AO2">
+        <v>-1.24609375</v>
       </c>
       <c r="AP2">
-        <v>1.985915492957746</v>
+        <v>3.043252595155709</v>
+      </c>
+      <c r="AQ2">
+        <v>-1.24609375</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S.C. Comcm S.A. (BVB:CMCM)</t>
+          <t>Mecanica Fina SA (BVB:MECE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,34 +721,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.153</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.902676399026764</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="H3">
-        <v>-0.902676399026764</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="I3">
-        <v>-0.5790754257907542</v>
+        <v>0.2502808988764045</v>
       </c>
       <c r="J3">
-        <v>-0.5790754257907542</v>
+        <v>0.2321153497644074</v>
       </c>
       <c r="K3">
-        <v>-0.229</v>
+        <v>1.15</v>
       </c>
       <c r="L3">
-        <v>-0.5571776155717763</v>
+        <v>0.3230337078651685</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.044</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.00176</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.03826086956521739</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,73 +757,8916 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.044</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.141</v>
+        <v>0.011</v>
       </c>
       <c r="V3">
-        <v>0.01305555555555555</v>
+        <v>0.00044</v>
       </c>
       <c r="W3">
-        <v>-0.01186528497409326</v>
+        <v>0.03091397849462365</v>
       </c>
       <c r="X3">
-        <v>0.05379899011795157</v>
+        <v>0.0979935407633446</v>
       </c>
       <c r="Y3">
-        <v>-0.06566427509204484</v>
+        <v>-0.06707956226872094</v>
       </c>
       <c r="Z3">
-        <v>0.02162019989479221</v>
+        <v>0.08705433559935444</v>
       </c>
       <c r="AA3">
-        <v>-0.01251972645975802</v>
+        <v>0.02020664755615226</v>
       </c>
       <c r="AB3">
-        <v>0.05379899011795157</v>
+        <v>0.09500495156889432</v>
       </c>
       <c r="AC3">
-        <v>-0.06631871657770959</v>
+        <v>-0.07479830401274207</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AG3">
-        <v>-0.141</v>
+        <v>2.839</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1023339317773788</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.08108108108108109</v>
       </c>
       <c r="AJ3">
-        <v>-0.01322825781030115</v>
+        <v>0.101979237759977</v>
       </c>
       <c r="AK3">
-        <v>-0.007680156871289284</v>
+        <v>0.08079342041606194</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="AN3">
+        <v>1.875</v>
+      </c>
+      <c r="AO3">
+        <v>3.48046875</v>
+      </c>
+      <c r="AP3">
+        <v>1.867763157894737</v>
+      </c>
+      <c r="AQ3">
+        <v>3.48046875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S.C. Comcm S.A. (BVB:CMCM)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.204</v>
+      </c>
+      <c r="G4">
+        <v>-0.4004444444444444</v>
+      </c>
+      <c r="H4">
+        <v>-0.4004444444444444</v>
+      </c>
+      <c r="I4">
+        <v>-0.5377777777777778</v>
+      </c>
+      <c r="J4">
+        <v>-0.5377777777777778</v>
+      </c>
+      <c r="K4">
+        <v>-1.35</v>
+      </c>
+      <c r="L4">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="M4">
         <v>-0</v>
       </c>
-      <c r="AP3">
-        <v>1.985915492957746</v>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1.08</v>
+      </c>
+      <c r="V4">
+        <v>0.07248322147651007</v>
+      </c>
+      <c r="W4">
+        <v>-0.07297297297297298</v>
+      </c>
+      <c r="X4">
+        <v>0.09282053439014437</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1657935073631173</v>
+      </c>
+      <c r="Z4">
+        <v>0.1225556947546163</v>
+      </c>
+      <c r="AA4">
+        <v>-0.06590772917914918</v>
+      </c>
+      <c r="AB4">
+        <v>0.09282053439014437</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1587282635692935</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-1.08</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.07814761215629523</v>
+      </c>
+      <c r="AK4">
+        <v>-0.07758620689655173</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AP4">
+        <v>1.146496815286624</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mecanica Fina SA (BVB:MECE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVB:MECE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.102333931777379</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>27.5549411267631</v>
+      </c>
+      <c r="I2">
+        <v>27.839</v>
+      </c>
+      <c r="J2">
+        <v>29.2149411267631</v>
+      </c>
+      <c r="K2">
+        <v>2.85</v>
+      </c>
+      <c r="L2">
+        <v>1.671</v>
+      </c>
+      <c r="M2">
+        <v>0.0950049515688943</v>
+      </c>
+      <c r="N2">
+        <v>0.092357857259999</v>
+      </c>
+      <c r="O2">
+        <v>0.06878925688073401</v>
+      </c>
+      <c r="P2">
+        <v>0.039732</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0979935407633446</v>
+      </c>
+      <c r="T2">
+        <v>0.0957169545319138</v>
+      </c>
+      <c r="U2">
+        <v>0.609759400485885</v>
+      </c>
+      <c r="V2">
+        <v>0.586308026607415</v>
+      </c>
+      <c r="W2">
+        <v>11.41218877430309</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>25</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.08189197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.16</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.52</v>
+      </c>
+      <c r="AH2">
+        <v>0.618</v>
+      </c>
+      <c r="AI2">
+        <v>1.182</v>
+      </c>
+      <c r="AJ2">
+        <v>2.85</v>
+      </c>
+      <c r="AK2">
+        <v>2.85</v>
+      </c>
+      <c r="AL2">
+        <v>0.256</v>
+      </c>
+      <c r="AM2">
+        <v>2.85</v>
+      </c>
+      <c r="AN2">
+        <v>0.011</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09282053439014437</v>
+      </c>
+      <c r="C2">
+        <v>28.97571988644219</v>
+      </c>
+      <c r="D2">
+        <v>28.96471988644219</v>
+      </c>
+      <c r="E2">
+        <v>-2.85</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.011</v>
+      </c>
+      <c r="H2">
+        <v>25</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.52</v>
+      </c>
+      <c r="K2">
+        <v>0.618</v>
+      </c>
+      <c r="L2">
+        <v>0.902</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.902</v>
+      </c>
+      <c r="O2">
+        <v>0.14432</v>
+      </c>
+      <c r="P2">
+        <v>0.75768</v>
+      </c>
+      <c r="Q2">
+        <v>1.37568</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09282053439014437</v>
+      </c>
+      <c r="T2">
+        <v>0.5564716730724656</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.16</v>
+      </c>
+      <c r="W2">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09272998153512013</v>
+      </c>
+      <c r="C3">
+        <v>28.74585402289163</v>
+      </c>
+      <c r="D3">
+        <v>29.01335402289163</v>
+      </c>
+      <c r="E3">
+        <v>-2.5715</v>
+      </c>
+      <c r="F3">
+        <v>0.2785</v>
+      </c>
+      <c r="G3">
+        <v>0.011</v>
+      </c>
+      <c r="H3">
+        <v>25</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.52</v>
+      </c>
+      <c r="K3">
+        <v>0.618</v>
+      </c>
+      <c r="L3">
+        <v>0.902</v>
+      </c>
+      <c r="M3">
+        <v>0.01272745</v>
+      </c>
+      <c r="N3">
+        <v>0.8892725500000001</v>
+      </c>
+      <c r="O3">
+        <v>0.142283608</v>
+      </c>
+      <c r="P3">
+        <v>0.746988942</v>
+      </c>
+      <c r="Q3">
+        <v>1.364988942</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09327889043951529</v>
+      </c>
+      <c r="T3">
+        <v>0.5611932509045956</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.16</v>
+      </c>
+      <c r="W3">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>70.87044144742268</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09263942868009592</v>
+      </c>
+      <c r="C4">
+        <v>28.51615175542724</v>
+      </c>
+      <c r="D4">
+        <v>29.06215175542724</v>
+      </c>
+      <c r="E4">
+        <v>-2.293</v>
+      </c>
+      <c r="F4">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.011</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.52</v>
+      </c>
+      <c r="K4">
+        <v>0.618</v>
+      </c>
+      <c r="L4">
+        <v>0.902</v>
+      </c>
+      <c r="M4">
+        <v>0.02545490000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.8765451</v>
+      </c>
+      <c r="O4">
+        <v>0.140247216</v>
+      </c>
+      <c r="P4">
+        <v>0.736297884</v>
+      </c>
+      <c r="Q4">
+        <v>1.354297884</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09374660069397542</v>
+      </c>
+      <c r="T4">
+        <v>0.5660111874679936</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.16</v>
+      </c>
+      <c r="W4">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>35.43522072371134</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09254887582507167</v>
+      </c>
+      <c r="C5">
+        <v>28.28661391089942</v>
+      </c>
+      <c r="D5">
+        <v>29.11111391089942</v>
+      </c>
+      <c r="E5">
+        <v>-2.0145</v>
+      </c>
+      <c r="F5">
+        <v>0.8355</v>
+      </c>
+      <c r="G5">
+        <v>0.011</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.52</v>
+      </c>
+      <c r="K5">
+        <v>0.618</v>
+      </c>
+      <c r="L5">
+        <v>0.902</v>
+      </c>
+      <c r="M5">
+        <v>0.03818235</v>
+      </c>
+      <c r="N5">
+        <v>0.86381765</v>
+      </c>
+      <c r="O5">
+        <v>0.138210824</v>
+      </c>
+      <c r="P5">
+        <v>0.7256068259999999</v>
+      </c>
+      <c r="Q5">
+        <v>1.343606826</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09422395445883677</v>
+      </c>
+      <c r="T5">
+        <v>0.5709284629296059</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.16</v>
+      </c>
+      <c r="W5">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>23.62348048247423</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09245832297004743</v>
+      </c>
+      <c r="C6">
+        <v>28.05724132174003</v>
+      </c>
+      <c r="D6">
+        <v>29.16024132174003</v>
+      </c>
+      <c r="E6">
+        <v>-1.736</v>
+      </c>
+      <c r="F6">
+        <v>1.114</v>
+      </c>
+      <c r="G6">
+        <v>0.011</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.52</v>
+      </c>
+      <c r="K6">
+        <v>0.618</v>
+      </c>
+      <c r="L6">
+        <v>0.902</v>
+      </c>
+      <c r="M6">
+        <v>0.05090980000000001</v>
+      </c>
+      <c r="N6">
+        <v>0.8510902</v>
+      </c>
+      <c r="O6">
+        <v>0.136174432</v>
+      </c>
+      <c r="P6">
+        <v>0.714915768</v>
+      </c>
+      <c r="Q6">
+        <v>1.332915768</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09471125309379941</v>
+      </c>
+      <c r="T6">
+        <v>0.5759481816300018</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.16</v>
+      </c>
+      <c r="W6">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>17.71761036185567</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0923677701150232</v>
+      </c>
+      <c r="C7">
+        <v>27.82803482600965</v>
+      </c>
+      <c r="D7">
+        <v>29.20953482600965</v>
+      </c>
+      <c r="E7">
+        <v>-1.4575</v>
+      </c>
+      <c r="F7">
+        <v>1.3925</v>
+      </c>
+      <c r="G7">
+        <v>0.011</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.52</v>
+      </c>
+      <c r="K7">
+        <v>0.618</v>
+      </c>
+      <c r="L7">
+        <v>0.902</v>
+      </c>
+      <c r="M7">
+        <v>0.06363725000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.83836275</v>
+      </c>
+      <c r="O7">
+        <v>0.13413804</v>
+      </c>
+      <c r="P7">
+        <v>0.70422471</v>
+      </c>
+      <c r="Q7">
+        <v>1.32222471</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09520881064739285</v>
+      </c>
+      <c r="T7">
+        <v>0.5810735786188272</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.16</v>
+      </c>
+      <c r="W7">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>14.17408828948454</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09235785725999898</v>
+      </c>
+      <c r="C8">
+        <v>27.55494112676305</v>
+      </c>
+      <c r="D8">
+        <v>29.21494112676305</v>
+      </c>
+      <c r="E8">
+        <v>-1.179</v>
+      </c>
+      <c r="F8">
+        <v>1.671</v>
+      </c>
+      <c r="G8">
+        <v>0.011</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.52</v>
+      </c>
+      <c r="K8">
+        <v>0.618</v>
+      </c>
+      <c r="L8">
+        <v>0.902</v>
+      </c>
+      <c r="M8">
+        <v>0.07903830000000001</v>
+      </c>
+      <c r="N8">
+        <v>0.8229617</v>
+      </c>
+      <c r="O8">
+        <v>0.131673872</v>
+      </c>
+      <c r="P8">
+        <v>0.691287828</v>
+      </c>
+      <c r="Q8">
+        <v>1.309287828</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09571695453191381</v>
+      </c>
+      <c r="T8">
+        <v>0.5863080266074149</v>
+      </c>
+      <c r="U8">
+        <v>0.0473</v>
+      </c>
+      <c r="V8">
+        <v>0.16</v>
+      </c>
+      <c r="W8">
+        <v>0.039732</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.41218877430309</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09250418440497474</v>
+      </c>
+      <c r="C9">
+        <v>27.19683952824556</v>
+      </c>
+      <c r="D9">
+        <v>29.13533952824556</v>
+      </c>
+      <c r="E9">
+        <v>-0.9004999999999999</v>
+      </c>
+      <c r="F9">
+        <v>1.9495</v>
+      </c>
+      <c r="G9">
+        <v>0.011</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.52</v>
+      </c>
+      <c r="K9">
+        <v>0.618</v>
+      </c>
+      <c r="L9">
+        <v>0.902</v>
+      </c>
+      <c r="M9">
+        <v>0.09961945000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.80238055</v>
+      </c>
+      <c r="O9">
+        <v>0.128380888</v>
+      </c>
+      <c r="P9">
+        <v>0.6739996619999999</v>
+      </c>
+      <c r="Q9">
+        <v>1.291999662</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09623602624190833</v>
+      </c>
+      <c r="T9">
+        <v>0.5916550433699506</v>
+      </c>
+      <c r="U9">
+        <v>0.0511</v>
+      </c>
+      <c r="V9">
+        <v>0.16</v>
+      </c>
+      <c r="W9">
+        <v>0.042924</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>9.054456735105443</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09245899154995049</v>
+      </c>
+      <c r="C10">
+        <v>26.9428779911825</v>
+      </c>
+      <c r="D10">
+        <v>29.1598779911825</v>
+      </c>
+      <c r="E10">
+        <v>-0.6219999999999999</v>
+      </c>
+      <c r="F10">
+        <v>2.228</v>
+      </c>
+      <c r="G10">
+        <v>0.011</v>
+      </c>
+      <c r="H10">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.52</v>
+      </c>
+      <c r="K10">
+        <v>0.618</v>
+      </c>
+      <c r="L10">
+        <v>0.902</v>
+      </c>
+      <c r="M10">
+        <v>0.1138508</v>
+      </c>
+      <c r="N10">
+        <v>0.7881492</v>
+      </c>
+      <c r="O10">
+        <v>0.126103872</v>
+      </c>
+      <c r="P10">
+        <v>0.6620453279999999</v>
+      </c>
+      <c r="Q10">
+        <v>1.280045328</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09676638211951141</v>
+      </c>
+      <c r="T10">
+        <v>0.5971182996273239</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0.16</v>
+      </c>
+      <c r="W10">
+        <v>0.042924</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>7.922649643217262</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0925574386949263</v>
+      </c>
+      <c r="C11">
+        <v>26.61097688417727</v>
+      </c>
+      <c r="D11">
+        <v>29.10647688417727</v>
+      </c>
+      <c r="E11">
+        <v>-0.3435000000000001</v>
+      </c>
+      <c r="F11">
+        <v>2.5065</v>
+      </c>
+      <c r="G11">
+        <v>0.011</v>
+      </c>
+      <c r="H11">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.52</v>
+      </c>
+      <c r="K11">
+        <v>0.618</v>
+      </c>
+      <c r="L11">
+        <v>0.902</v>
+      </c>
+      <c r="M11">
+        <v>0.1328445</v>
+      </c>
+      <c r="N11">
+        <v>0.7691555</v>
+      </c>
+      <c r="O11">
+        <v>0.12306488</v>
+      </c>
+      <c r="P11">
+        <v>0.6460906199999999</v>
+      </c>
+      <c r="Q11">
+        <v>1.26409062</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09730839417024867</v>
+      </c>
+      <c r="T11">
+        <v>0.6027016274507935</v>
+      </c>
+      <c r="U11">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.16</v>
+      </c>
+      <c r="W11">
+        <v>0.04452</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.789893446849511</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09269620583990205</v>
+      </c>
+      <c r="C12">
+        <v>26.25753612286436</v>
+      </c>
+      <c r="D12">
+        <v>29.03153612286436</v>
+      </c>
+      <c r="E12">
+        <v>-0.06499999999999995</v>
+      </c>
+      <c r="F12">
+        <v>2.785</v>
+      </c>
+      <c r="G12">
+        <v>0.011</v>
+      </c>
+      <c r="H12">
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.52</v>
+      </c>
+      <c r="K12">
+        <v>0.618</v>
+      </c>
+      <c r="L12">
+        <v>0.902</v>
+      </c>
+      <c r="M12">
+        <v>0.153175</v>
+      </c>
+      <c r="N12">
+        <v>0.7488250000000001</v>
+      </c>
+      <c r="O12">
+        <v>0.119812</v>
+      </c>
+      <c r="P12">
+        <v>0.629013</v>
+      </c>
+      <c r="Q12">
+        <v>1.247013</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0978624509332245</v>
+      </c>
+      <c r="T12">
+        <v>0.6084090292258957</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.16</v>
+      </c>
+      <c r="W12">
+        <v>0.0462</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>5.888689407540395</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09268377298487783</v>
+      </c>
+      <c r="C13">
+        <v>25.98573470501166</v>
+      </c>
+      <c r="D13">
+        <v>29.03823470501166</v>
+      </c>
+      <c r="E13">
+        <v>0.2135000000000002</v>
+      </c>
+      <c r="F13">
+        <v>3.0635</v>
+      </c>
+      <c r="G13">
+        <v>0.011</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.52</v>
+      </c>
+      <c r="K13">
+        <v>0.618</v>
+      </c>
+      <c r="L13">
+        <v>0.902</v>
+      </c>
+      <c r="M13">
+        <v>0.1684925</v>
+      </c>
+      <c r="N13">
+        <v>0.7335075</v>
+      </c>
+      <c r="O13">
+        <v>0.1173612</v>
+      </c>
+      <c r="P13">
+        <v>0.6161462999999999</v>
+      </c>
+      <c r="Q13">
+        <v>1.2341463</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09842895840997508</v>
+      </c>
+      <c r="T13">
+        <v>0.6142446872206632</v>
+      </c>
+      <c r="U13">
+        <v>0.055</v>
+      </c>
+      <c r="V13">
+        <v>0.16</v>
+      </c>
+      <c r="W13">
+        <v>0.0462</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.353354006854904</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09267134012985359</v>
+      </c>
+      <c r="C14">
+        <v>25.71393637906278</v>
+      </c>
+      <c r="D14">
+        <v>29.04493637906278</v>
+      </c>
+      <c r="E14">
+        <v>0.492</v>
+      </c>
+      <c r="F14">
+        <v>3.342</v>
+      </c>
+      <c r="G14">
+        <v>0.011</v>
+      </c>
+      <c r="H14">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.52</v>
+      </c>
+      <c r="K14">
+        <v>0.618</v>
+      </c>
+      <c r="L14">
+        <v>0.902</v>
+      </c>
+      <c r="M14">
+        <v>0.18381</v>
+      </c>
+      <c r="N14">
+        <v>0.71819</v>
+      </c>
+      <c r="O14">
+        <v>0.1149104</v>
+      </c>
+      <c r="P14">
+        <v>0.6032796</v>
+      </c>
+      <c r="Q14">
+        <v>1.2212796</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09900834105665181</v>
+      </c>
+      <c r="T14">
+        <v>0.6202129738062208</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.16</v>
+      </c>
+      <c r="W14">
+        <v>0.0462</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>4.907241172950329</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09265890727482935</v>
+      </c>
+      <c r="C15">
+        <v>25.44214114715892</v>
+      </c>
+      <c r="D15">
+        <v>29.05164114715892</v>
+      </c>
+      <c r="E15">
+        <v>0.7705000000000002</v>
+      </c>
+      <c r="F15">
+        <v>3.6205</v>
+      </c>
+      <c r="G15">
+        <v>0.011</v>
+      </c>
+      <c r="H15">
+        <v>25</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.52</v>
+      </c>
+      <c r="K15">
+        <v>0.618</v>
+      </c>
+      <c r="L15">
+        <v>0.902</v>
+      </c>
+      <c r="M15">
+        <v>0.1991275</v>
+      </c>
+      <c r="N15">
+        <v>0.7028725</v>
+      </c>
+      <c r="O15">
+        <v>0.1124596</v>
+      </c>
+      <c r="P15">
+        <v>0.5904129</v>
+      </c>
+      <c r="Q15">
+        <v>1.2084129</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09960104284463145</v>
+      </c>
+      <c r="T15">
+        <v>0.626318462382251</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.16</v>
+      </c>
+      <c r="W15">
+        <v>0.0462</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.529761082723381</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09358727441980515</v>
+      </c>
+      <c r="C16">
+        <v>24.67136279540175</v>
+      </c>
+      <c r="D16">
+        <v>28.55936279540175</v>
+      </c>
+      <c r="E16">
+        <v>1.049</v>
+      </c>
+      <c r="F16">
+        <v>3.899</v>
+      </c>
+      <c r="G16">
+        <v>0.011</v>
+      </c>
+      <c r="H16">
+        <v>25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.52</v>
+      </c>
+      <c r="K16">
+        <v>0.618</v>
+      </c>
+      <c r="L16">
+        <v>0.902</v>
+      </c>
+      <c r="M16">
+        <v>0.245637</v>
+      </c>
+      <c r="N16">
+        <v>0.656363</v>
+      </c>
+      <c r="O16">
+        <v>0.10501808</v>
+      </c>
+      <c r="P16">
+        <v>0.55134492</v>
+      </c>
+      <c r="Q16">
+        <v>1.16934492</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1002075283951223</v>
+      </c>
+      <c r="T16">
+        <v>0.6325659390647005</v>
+      </c>
+      <c r="U16">
+        <v>0.063</v>
+      </c>
+      <c r="V16">
+        <v>0.16</v>
+      </c>
+      <c r="W16">
+        <v>0.05292</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>3.67208523145943</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09453664156478089</v>
+      </c>
+      <c r="C17">
+        <v>23.90640864319231</v>
+      </c>
+      <c r="D17">
+        <v>28.07290864319231</v>
+      </c>
+      <c r="E17">
+        <v>1.3275</v>
+      </c>
+      <c r="F17">
+        <v>4.1775</v>
+      </c>
+      <c r="G17">
+        <v>0.011</v>
+      </c>
+      <c r="H17">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.52</v>
+      </c>
+      <c r="K17">
+        <v>0.618</v>
+      </c>
+      <c r="L17">
+        <v>0.902</v>
+      </c>
+      <c r="M17">
+        <v>0.29284275</v>
+      </c>
+      <c r="N17">
+        <v>0.60915725</v>
+      </c>
+      <c r="O17">
+        <v>0.09746516000000002</v>
+      </c>
+      <c r="P17">
+        <v>0.5116920899999999</v>
+      </c>
+      <c r="Q17">
+        <v>1.12969209</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1008282841938599</v>
+      </c>
+      <c r="T17">
+        <v>0.6389604151985017</v>
+      </c>
+      <c r="U17">
+        <v>0.0701</v>
+      </c>
+      <c r="V17">
+        <v>0.16</v>
+      </c>
+      <c r="W17">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>3.080151378171391</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09751376870975666</v>
+      </c>
+      <c r="C18">
+        <v>22.20445005423301</v>
+      </c>
+      <c r="D18">
+        <v>26.64945005423301</v>
+      </c>
+      <c r="E18">
+        <v>1.606</v>
+      </c>
+      <c r="F18">
+        <v>4.456</v>
+      </c>
+      <c r="G18">
+        <v>0.011</v>
+      </c>
+      <c r="H18">
+        <v>25</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.52</v>
+      </c>
+      <c r="K18">
+        <v>0.618</v>
+      </c>
+      <c r="L18">
+        <v>0.902</v>
+      </c>
+      <c r="M18">
+        <v>0.4072784000000001</v>
+      </c>
+      <c r="N18">
+        <v>0.4947215999999999</v>
+      </c>
+      <c r="O18">
+        <v>0.079155456</v>
+      </c>
+      <c r="P18">
+        <v>0.4155661439999999</v>
+      </c>
+      <c r="Q18">
+        <v>1.033566144</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1014638198925674</v>
+      </c>
+      <c r="T18">
+        <v>0.64550714076406</v>
+      </c>
+      <c r="U18">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.16</v>
+      </c>
+      <c r="W18">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>2.214701295231959</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09780709585473243</v>
+      </c>
+      <c r="C19">
+        <v>21.79347434116238</v>
+      </c>
+      <c r="D19">
+        <v>26.51697434116238</v>
+      </c>
+      <c r="E19">
+        <v>1.884500000000001</v>
+      </c>
+      <c r="F19">
+        <v>4.734500000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.011</v>
+      </c>
+      <c r="H19">
+        <v>25</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.52</v>
+      </c>
+      <c r="K19">
+        <v>0.618</v>
+      </c>
+      <c r="L19">
+        <v>0.902</v>
+      </c>
+      <c r="M19">
+        <v>0.4327333000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.4692666999999999</v>
+      </c>
+      <c r="O19">
+        <v>0.075082672</v>
+      </c>
+      <c r="P19">
+        <v>0.3941840279999999</v>
+      </c>
+      <c r="Q19">
+        <v>1.012184028</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1021146697044969</v>
+      </c>
+      <c r="T19">
+        <v>0.652211618752885</v>
+      </c>
+      <c r="U19">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.16</v>
+      </c>
+      <c r="W19">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>2.084424748453608</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1012907429997082</v>
+      </c>
+      <c r="C20">
+        <v>20.03674288602642</v>
+      </c>
+      <c r="D20">
+        <v>25.03874288602642</v>
+      </c>
+      <c r="E20">
+        <v>2.163</v>
+      </c>
+      <c r="F20">
+        <v>5.013</v>
+      </c>
+      <c r="G20">
+        <v>0.011</v>
+      </c>
+      <c r="H20">
+        <v>25</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.52</v>
+      </c>
+      <c r="K20">
+        <v>0.618</v>
+      </c>
+      <c r="L20">
+        <v>0.902</v>
+      </c>
+      <c r="M20">
+        <v>0.5639625</v>
+      </c>
+      <c r="N20">
+        <v>0.3380375</v>
+      </c>
+      <c r="O20">
+        <v>0.05408600000000001</v>
+      </c>
+      <c r="P20">
+        <v>0.2839515</v>
+      </c>
+      <c r="Q20">
+        <v>0.9019515</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1027813939020832</v>
+      </c>
+      <c r="T20">
+        <v>0.6590796205950958</v>
+      </c>
+      <c r="U20">
+        <v>0.1125</v>
+      </c>
+      <c r="V20">
+        <v>0.16</v>
+      </c>
+      <c r="W20">
+        <v>0.0945</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>1.599397123035663</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.101761310144684</v>
+      </c>
+      <c r="C21">
+        <v>19.57110558334667</v>
+      </c>
+      <c r="D21">
+        <v>24.85160558334667</v>
+      </c>
+      <c r="E21">
+        <v>2.4415</v>
+      </c>
+      <c r="F21">
+        <v>5.2915</v>
+      </c>
+      <c r="G21">
+        <v>0.011</v>
+      </c>
+      <c r="H21">
+        <v>25</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.52</v>
+      </c>
+      <c r="K21">
+        <v>0.618</v>
+      </c>
+      <c r="L21">
+        <v>0.902</v>
+      </c>
+      <c r="M21">
+        <v>0.5952937500000001</v>
+      </c>
+      <c r="N21">
+        <v>0.30670625</v>
+      </c>
+      <c r="O21">
+        <v>0.04907300000000001</v>
+      </c>
+      <c r="P21">
+        <v>0.2576332499999999</v>
+      </c>
+      <c r="Q21">
+        <v>0.8756332499999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1034645804255358</v>
+      </c>
+      <c r="T21">
+        <v>0.6661172027297069</v>
+      </c>
+      <c r="U21">
+        <v>0.1125</v>
+      </c>
+      <c r="V21">
+        <v>0.16</v>
+      </c>
+      <c r="W21">
+        <v>0.0945</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>1.515218327086417</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1177745969138762</v>
+      </c>
+      <c r="C22">
+        <v>14.2535689509094</v>
+      </c>
+      <c r="D22">
+        <v>19.8125689509094</v>
+      </c>
+      <c r="E22">
+        <v>2.72</v>
+      </c>
+      <c r="F22">
+        <v>5.57</v>
+      </c>
+      <c r="G22">
+        <v>0.011</v>
+      </c>
+      <c r="H22">
+        <v>25</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.52</v>
+      </c>
+      <c r="K22">
+        <v>0.618</v>
+      </c>
+      <c r="L22">
+        <v>0.902</v>
+      </c>
+      <c r="M22">
+        <v>1.095062</v>
+      </c>
+      <c r="N22">
+        <v>-0.193062</v>
+      </c>
+      <c r="O22">
+        <v>-0.03088992</v>
+      </c>
+      <c r="P22">
+        <v>-0.16217208</v>
+      </c>
+      <c r="Q22">
+        <v>0.4558279200000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1045458044906397</v>
+      </c>
+      <c r="T22">
+        <v>0.6772550148833087</v>
+      </c>
+      <c r="U22">
+        <v>0.1966</v>
+      </c>
+      <c r="V22">
+        <v>0.1317916245838135</v>
+      </c>
+      <c r="W22">
+        <v>0.1706897666068223</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.8236976536488345</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1230791475299627</v>
+      </c>
+      <c r="C23">
+        <v>12.72806090781738</v>
+      </c>
+      <c r="D23">
+        <v>18.56556090781738</v>
+      </c>
+      <c r="E23">
+        <v>2.9985</v>
+      </c>
+      <c r="F23">
+        <v>5.8485</v>
+      </c>
+      <c r="G23">
+        <v>0.011</v>
+      </c>
+      <c r="H23">
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.52</v>
+      </c>
+      <c r="K23">
+        <v>0.618</v>
+      </c>
+      <c r="L23">
+        <v>0.902</v>
+      </c>
+      <c r="M23">
+        <v>1.2504093</v>
+      </c>
+      <c r="N23">
+        <v>-0.3484093</v>
+      </c>
+      <c r="O23">
+        <v>-0.05574548800000002</v>
+      </c>
+      <c r="P23">
+        <v>-0.292663812</v>
+      </c>
+      <c r="Q23">
+        <v>0.325336188</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1055230306437952</v>
+      </c>
+      <c r="T23">
+        <v>0.6873215327094599</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1154182074621486</v>
+      </c>
+      <c r="W23">
+        <v>0.1891235872445926</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.7213637966384288</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1248291475299627</v>
+      </c>
+      <c r="C24">
+        <v>12.07190132938945</v>
+      </c>
+      <c r="D24">
+        <v>18.18790132938945</v>
+      </c>
+      <c r="E24">
+        <v>3.277000000000001</v>
+      </c>
+      <c r="F24">
+        <v>6.127000000000001</v>
+      </c>
+      <c r="G24">
+        <v>0.011</v>
+      </c>
+      <c r="H24">
+        <v>25</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.52</v>
+      </c>
+      <c r="K24">
+        <v>0.618</v>
+      </c>
+      <c r="L24">
+        <v>0.902</v>
+      </c>
+      <c r="M24">
+        <v>1.3099526</v>
+      </c>
+      <c r="N24">
+        <v>-0.4079526000000001</v>
+      </c>
+      <c r="O24">
+        <v>-0.06527241600000003</v>
+      </c>
+      <c r="P24">
+        <v>-0.3426801840000001</v>
+      </c>
+      <c r="Q24">
+        <v>0.2753198159999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1063784541135875</v>
+      </c>
+      <c r="T24">
+        <v>0.6961333472313761</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.1101719253047782</v>
+      </c>
+      <c r="W24">
+        <v>0.1902452423698384</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.6885745331548637</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1265791475299627</v>
+      </c>
+      <c r="C25">
+        <v>11.43080009410669</v>
+      </c>
+      <c r="D25">
+        <v>17.82530009410669</v>
+      </c>
+      <c r="E25">
+        <v>3.555500000000001</v>
+      </c>
+      <c r="F25">
+        <v>6.405500000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.011</v>
+      </c>
+      <c r="H25">
+        <v>25</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.52</v>
+      </c>
+      <c r="K25">
+        <v>0.618</v>
+      </c>
+      <c r="L25">
+        <v>0.902</v>
+      </c>
+      <c r="M25">
+        <v>1.3694959</v>
+      </c>
+      <c r="N25">
+        <v>-0.4674959000000002</v>
+      </c>
+      <c r="O25">
+        <v>-0.07479934400000005</v>
+      </c>
+      <c r="P25">
+        <v>-0.3926965560000001</v>
+      </c>
+      <c r="Q25">
+        <v>0.2253034439999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1072560963748029</v>
+      </c>
+      <c r="T25">
+        <v>0.7051740400525628</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.1053818415958748</v>
+      </c>
+      <c r="W25">
+        <v>0.1912693622668019</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.6586365099742174</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1283291475299627</v>
+      </c>
+      <c r="C26">
+        <v>10.80387417891246</v>
+      </c>
+      <c r="D26">
+        <v>17.47687417891246</v>
+      </c>
+      <c r="E26">
+        <v>3.834</v>
+      </c>
+      <c r="F26">
+        <v>6.684</v>
+      </c>
+      <c r="G26">
+        <v>0.011</v>
+      </c>
+      <c r="H26">
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.52</v>
+      </c>
+      <c r="K26">
+        <v>0.618</v>
+      </c>
+      <c r="L26">
+        <v>0.902</v>
+      </c>
+      <c r="M26">
+        <v>1.4290392</v>
+      </c>
+      <c r="N26">
+        <v>-0.5270392</v>
+      </c>
+      <c r="O26">
+        <v>-0.08432627200000002</v>
+      </c>
+      <c r="P26">
+        <v>-0.442712928</v>
+      </c>
+      <c r="Q26">
+        <v>0.175287072</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1081568344849976</v>
+      </c>
+      <c r="T26">
+        <v>0.7144526458427281</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.10099093152938</v>
+      </c>
+      <c r="W26">
+        <v>0.1922081388390185</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.6311933220586251</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1300791475299627</v>
+      </c>
+      <c r="C27">
+        <v>10.19030827787458</v>
+      </c>
+      <c r="D27">
+        <v>17.14180827787458</v>
+      </c>
+      <c r="E27">
+        <v>4.112500000000001</v>
+      </c>
+      <c r="F27">
+        <v>6.9625</v>
+      </c>
+      <c r="G27">
+        <v>0.011</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.52</v>
+      </c>
+      <c r="K27">
+        <v>0.618</v>
+      </c>
+      <c r="L27">
+        <v>0.902</v>
+      </c>
+      <c r="M27">
+        <v>1.4885825</v>
+      </c>
+      <c r="N27">
+        <v>-0.5865824999999999</v>
+      </c>
+      <c r="O27">
+        <v>-0.0938532</v>
+      </c>
+      <c r="P27">
+        <v>-0.4927292999999999</v>
+      </c>
+      <c r="Q27">
+        <v>0.1252707000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.109081592278131</v>
+      </c>
+      <c r="T27">
+        <v>0.7239786811206311</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.09695129426820484</v>
+      </c>
+      <c r="W27">
+        <v>0.1930718132854578</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.6059455891762802</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1318291475299627</v>
+      </c>
+      <c r="C28">
+        <v>9.589348432946746</v>
+      </c>
+      <c r="D28">
+        <v>16.81934843294675</v>
+      </c>
+      <c r="E28">
+        <v>4.391</v>
+      </c>
+      <c r="F28">
+        <v>7.241000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.011</v>
+      </c>
+      <c r="H28">
+        <v>25</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.52</v>
+      </c>
+      <c r="K28">
+        <v>0.618</v>
+      </c>
+      <c r="L28">
+        <v>0.902</v>
+      </c>
+      <c r="M28">
+        <v>1.5481258</v>
+      </c>
+      <c r="N28">
+        <v>-0.6461258</v>
+      </c>
+      <c r="O28">
+        <v>-0.103380128</v>
+      </c>
+      <c r="P28">
+        <v>-0.5427456719999999</v>
+      </c>
+      <c r="Q28">
+        <v>0.07525432800000009</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1100313435251327</v>
+      </c>
+      <c r="T28">
+        <v>0.7337621768114505</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.09322239833481234</v>
+      </c>
+      <c r="W28">
+        <v>0.1938690512360171</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.5826399895925771</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1335791475299627</v>
+      </c>
+      <c r="C29">
+        <v>9.000296370338752</v>
+      </c>
+      <c r="D29">
+        <v>16.50879637033875</v>
+      </c>
+      <c r="E29">
+        <v>4.669500000000001</v>
+      </c>
+      <c r="F29">
+        <v>7.519500000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.011</v>
+      </c>
+      <c r="H29">
+        <v>25</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.52</v>
+      </c>
+      <c r="K29">
+        <v>0.618</v>
+      </c>
+      <c r="L29">
+        <v>0.902</v>
+      </c>
+      <c r="M29">
+        <v>1.6076691</v>
+      </c>
+      <c r="N29">
+        <v>-0.7056691</v>
+      </c>
+      <c r="O29">
+        <v>-0.112907056</v>
+      </c>
+      <c r="P29">
+        <v>-0.592762044</v>
+      </c>
+      <c r="Q29">
+        <v>0.02523795600000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1110071153542441</v>
+      </c>
+      <c r="T29">
+        <v>0.7438137134801005</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.08976971691500447</v>
+      </c>
+      <c r="W29">
+        <v>0.194607234523572</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5610607307187778</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1353291475299627</v>
+      </c>
+      <c r="C30">
+        <v>8.422504452950534</v>
+      </c>
+      <c r="D30">
+        <v>16.20950445295054</v>
+      </c>
+      <c r="E30">
+        <v>4.948</v>
+      </c>
+      <c r="F30">
+        <v>7.798000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.011</v>
+      </c>
+      <c r="H30">
+        <v>25</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.52</v>
+      </c>
+      <c r="K30">
+        <v>0.618</v>
+      </c>
+      <c r="L30">
+        <v>0.902</v>
+      </c>
+      <c r="M30">
+        <v>1.6672124</v>
+      </c>
+      <c r="N30">
+        <v>-0.7652124000000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.122433984</v>
+      </c>
+      <c r="P30">
+        <v>-0.6427784160000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.02477841600000008</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1120099919563864</v>
+      </c>
+      <c r="T30">
+        <v>0.7541444595006574</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.08656365559661144</v>
+      </c>
+      <c r="W30">
+        <v>0.1952926904334445</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5410228474788215</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1370791475299627</v>
+      </c>
+      <c r="C31">
+        <v>7.855371172080707</v>
+      </c>
+      <c r="D31">
+        <v>15.92087117208071</v>
+      </c>
+      <c r="E31">
+        <v>5.2265</v>
+      </c>
+      <c r="F31">
+        <v>8.076499999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.011</v>
+      </c>
+      <c r="H31">
+        <v>25</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.52</v>
+      </c>
+      <c r="K31">
+        <v>0.618</v>
+      </c>
+      <c r="L31">
+        <v>0.902</v>
+      </c>
+      <c r="M31">
+        <v>1.7267557</v>
+      </c>
+      <c r="N31">
+        <v>-0.8247556999999998</v>
+      </c>
+      <c r="O31">
+        <v>-0.131960912</v>
+      </c>
+      <c r="P31">
+        <v>-0.6927947879999998</v>
+      </c>
+      <c r="Q31">
+        <v>-0.07479478799999983</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1130411186036595</v>
+      </c>
+      <c r="T31">
+        <v>0.764766212451371</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.083578701955349</v>
+      </c>
+      <c r="W31">
+        <v>0.1959308735219464</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5223668872209313</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1388291475299627</v>
+      </c>
+      <c r="C32">
+        <v>7.298337112367802</v>
+      </c>
+      <c r="D32">
+        <v>15.6423371123678</v>
+      </c>
+      <c r="E32">
+        <v>5.505000000000001</v>
+      </c>
+      <c r="F32">
+        <v>8.355</v>
+      </c>
+      <c r="G32">
+        <v>0.011</v>
+      </c>
+      <c r="H32">
+        <v>25</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.52</v>
+      </c>
+      <c r="K32">
+        <v>0.618</v>
+      </c>
+      <c r="L32">
+        <v>0.902</v>
+      </c>
+      <c r="M32">
+        <v>1.786299</v>
+      </c>
+      <c r="N32">
+        <v>-0.8842990000000001</v>
+      </c>
+      <c r="O32">
+        <v>-0.14148784</v>
+      </c>
+      <c r="P32">
+        <v>-0.74281116</v>
+      </c>
+      <c r="Q32">
+        <v>-0.12481116</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1141017060122832</v>
+      </c>
+      <c r="T32">
+        <v>0.7756914440578191</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.08079274522350402</v>
+      </c>
+      <c r="W32">
+        <v>0.1965265110712148</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5049546576469001</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1484662225070927</v>
+      </c>
+      <c r="C33">
+        <v>5.645244533876438</v>
+      </c>
+      <c r="D33">
+        <v>14.26774453387644</v>
+      </c>
+      <c r="E33">
+        <v>5.7835</v>
+      </c>
+      <c r="F33">
+        <v>8.6335</v>
+      </c>
+      <c r="G33">
+        <v>0.011</v>
+      </c>
+      <c r="H33">
+        <v>25</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.52</v>
+      </c>
+      <c r="K33">
+        <v>0.618</v>
+      </c>
+      <c r="L33">
+        <v>0.902</v>
+      </c>
+      <c r="M33">
+        <v>2.0616798</v>
+      </c>
+      <c r="N33">
+        <v>-1.1596798</v>
+      </c>
+      <c r="O33">
+        <v>-0.185548768</v>
+      </c>
+      <c r="P33">
+        <v>-0.9741310319999997</v>
+      </c>
+      <c r="Q33">
+        <v>-0.3561310319999997</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1153916944720699</v>
+      </c>
+      <c r="T33">
+        <v>0.7889797620014617</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07000117088987341</v>
+      </c>
+      <c r="W33">
+        <v>0.2220837203914982</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.4375073180617088</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1504662225070927</v>
+      </c>
+      <c r="C34">
+        <v>5.111201824298879</v>
+      </c>
+      <c r="D34">
+        <v>14.01220182429888</v>
+      </c>
+      <c r="E34">
+        <v>6.062000000000001</v>
+      </c>
+      <c r="F34">
+        <v>8.912000000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.011</v>
+      </c>
+      <c r="H34">
+        <v>25</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.52</v>
+      </c>
+      <c r="K34">
+        <v>0.618</v>
+      </c>
+      <c r="L34">
+        <v>0.902</v>
+      </c>
+      <c r="M34">
+        <v>2.1281856</v>
+      </c>
+      <c r="N34">
+        <v>-1.2261856</v>
+      </c>
+      <c r="O34">
+        <v>-0.196189696</v>
+      </c>
+      <c r="P34">
+        <v>-1.029995904</v>
+      </c>
+      <c r="Q34">
+        <v>-0.411995904</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1165180429201886</v>
+      </c>
+      <c r="T34">
+        <v>0.8005824055603068</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.06781363429956486</v>
+      </c>
+      <c r="W34">
+        <v>0.2226061041292639</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4238352143722803</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1524662225070927</v>
+      </c>
+      <c r="C35">
+        <v>4.58615185518339</v>
+      </c>
+      <c r="D35">
+        <v>13.76565185518339</v>
+      </c>
+      <c r="E35">
+        <v>6.3405</v>
+      </c>
+      <c r="F35">
+        <v>9.1905</v>
+      </c>
+      <c r="G35">
+        <v>0.011</v>
+      </c>
+      <c r="H35">
+        <v>25</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.52</v>
+      </c>
+      <c r="K35">
+        <v>0.618</v>
+      </c>
+      <c r="L35">
+        <v>0.902</v>
+      </c>
+      <c r="M35">
+        <v>2.1946914</v>
+      </c>
+      <c r="N35">
+        <v>-1.2926914</v>
+      </c>
+      <c r="O35">
+        <v>-0.206830624</v>
+      </c>
+      <c r="P35">
+        <v>-1.085860776</v>
+      </c>
+      <c r="Q35">
+        <v>-0.4678607759999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1176780137100422</v>
+      </c>
+      <c r="T35">
+        <v>0.8125313966880726</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.06575867568442655</v>
+      </c>
+      <c r="W35">
+        <v>0.223096828246559</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.4109917230276658</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1544662225070927</v>
+      </c>
+      <c r="C36">
+        <v>4.069628142524508</v>
+      </c>
+      <c r="D36">
+        <v>13.52762814252451</v>
+      </c>
+      <c r="E36">
+        <v>6.619000000000002</v>
+      </c>
+      <c r="F36">
+        <v>9.469000000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.011</v>
+      </c>
+      <c r="H36">
+        <v>25</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.52</v>
+      </c>
+      <c r="K36">
+        <v>0.618</v>
+      </c>
+      <c r="L36">
+        <v>0.902</v>
+      </c>
+      <c r="M36">
+        <v>2.2611972</v>
+      </c>
+      <c r="N36">
+        <v>-1.3591972</v>
+      </c>
+      <c r="O36">
+        <v>-0.2174715520000001</v>
+      </c>
+      <c r="P36">
+        <v>-1.141725648</v>
+      </c>
+      <c r="Q36">
+        <v>-0.523725648</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1188731351298913</v>
+      </c>
+      <c r="T36">
+        <v>0.8248424784560736</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.06382459698782575</v>
+      </c>
+      <c r="W36">
+        <v>0.2235586862393072</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3989037311739109</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1564662225070927</v>
+      </c>
+      <c r="C37">
+        <v>3.561195918062909</v>
+      </c>
+      <c r="D37">
+        <v>13.29769591806291</v>
+      </c>
+      <c r="E37">
+        <v>6.897500000000003</v>
+      </c>
+      <c r="F37">
+        <v>9.747500000000002</v>
+      </c>
+      <c r="G37">
+        <v>0.011</v>
+      </c>
+      <c r="H37">
+        <v>25</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.52</v>
+      </c>
+      <c r="K37">
+        <v>0.618</v>
+      </c>
+      <c r="L37">
+        <v>0.902</v>
+      </c>
+      <c r="M37">
+        <v>2.327703000000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.425703</v>
+      </c>
+      <c r="O37">
+        <v>-0.2281124800000001</v>
+      </c>
+      <c r="P37">
+        <v>-1.19759052</v>
+      </c>
+      <c r="Q37">
+        <v>-0.5795905200000003</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.120105029516505</v>
+      </c>
+      <c r="T37">
+        <v>0.8375323627400132</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06200103707388786</v>
+      </c>
+      <c r="W37">
+        <v>0.2239941523467556</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3875064817117991</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1584662225070927</v>
+      </c>
+      <c r="C38">
+        <v>3.060449478934702</v>
+      </c>
+      <c r="D38">
+        <v>13.0754494789347</v>
+      </c>
+      <c r="E38">
+        <v>7.176</v>
+      </c>
+      <c r="F38">
+        <v>10.026</v>
+      </c>
+      <c r="G38">
+        <v>0.011</v>
+      </c>
+      <c r="H38">
+        <v>25</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.52</v>
+      </c>
+      <c r="K38">
+        <v>0.618</v>
+      </c>
+      <c r="L38">
+        <v>0.902</v>
+      </c>
+      <c r="M38">
+        <v>2.3942088</v>
+      </c>
+      <c r="N38">
+        <v>-1.4922088</v>
+      </c>
+      <c r="O38">
+        <v>-0.238753408</v>
+      </c>
+      <c r="P38">
+        <v>-1.253455392</v>
+      </c>
+      <c r="Q38">
+        <v>-0.6354553919999998</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1213754206027004</v>
+      </c>
+      <c r="T38">
+        <v>0.8506188059078258</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06027878604405766</v>
+      </c>
+      <c r="W38">
+        <v>0.224405425892679</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3767424127753604</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1604662225070927</v>
+      </c>
+      <c r="C39">
+        <v>2.567009798726042</v>
+      </c>
+      <c r="D39">
+        <v>12.86050979872604</v>
+      </c>
+      <c r="E39">
+        <v>7.454500000000001</v>
+      </c>
+      <c r="F39">
+        <v>10.3045</v>
+      </c>
+      <c r="G39">
+        <v>0.011</v>
+      </c>
+      <c r="H39">
+        <v>25</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.52</v>
+      </c>
+      <c r="K39">
+        <v>0.618</v>
+      </c>
+      <c r="L39">
+        <v>0.902</v>
+      </c>
+      <c r="M39">
+        <v>2.4607146</v>
+      </c>
+      <c r="N39">
+        <v>-1.5587146</v>
+      </c>
+      <c r="O39">
+        <v>-0.249394336</v>
+      </c>
+      <c r="P39">
+        <v>-1.309320264</v>
+      </c>
+      <c r="Q39">
+        <v>-0.6913202640000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.122686141564648</v>
+      </c>
+      <c r="T39">
+        <v>0.8641206917158867</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.05864962966448853</v>
+      </c>
+      <c r="W39">
+        <v>0.2247944684361202</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3665601854030532</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1624662225070927</v>
+      </c>
+      <c r="C40">
+        <v>2.080522370340118</v>
+      </c>
+      <c r="D40">
+        <v>12.65252237034012</v>
+      </c>
+      <c r="E40">
+        <v>7.733000000000001</v>
+      </c>
+      <c r="F40">
+        <v>10.583</v>
+      </c>
+      <c r="G40">
+        <v>0.011</v>
+      </c>
+      <c r="H40">
+        <v>25</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.52</v>
+      </c>
+      <c r="K40">
+        <v>0.618</v>
+      </c>
+      <c r="L40">
+        <v>0.902</v>
+      </c>
+      <c r="M40">
+        <v>2.5272204</v>
+      </c>
+      <c r="N40">
+        <v>-1.6252204</v>
+      </c>
+      <c r="O40">
+        <v>-0.260035264</v>
+      </c>
+      <c r="P40">
+        <v>-1.365185136</v>
+      </c>
+      <c r="Q40">
+        <v>-0.7471851359999998</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1240391438479488</v>
+      </c>
+      <c r="T40">
+        <v>0.8780581222274332</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.05710621835752831</v>
+      </c>
+      <c r="W40">
+        <v>0.2251630350562223</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3569138647345519</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1644662225070927</v>
+      </c>
+      <c r="C41">
+        <v>1.600655254850894</v>
+      </c>
+      <c r="D41">
+        <v>12.4511552548509</v>
+      </c>
+      <c r="E41">
+        <v>8.011500000000002</v>
+      </c>
+      <c r="F41">
+        <v>10.8615</v>
+      </c>
+      <c r="G41">
+        <v>0.011</v>
+      </c>
+      <c r="H41">
+        <v>25</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.52</v>
+      </c>
+      <c r="K41">
+        <v>0.618</v>
+      </c>
+      <c r="L41">
+        <v>0.902</v>
+      </c>
+      <c r="M41">
+        <v>2.5937262</v>
+      </c>
+      <c r="N41">
+        <v>-1.6917262</v>
+      </c>
+      <c r="O41">
+        <v>-0.2706761920000001</v>
+      </c>
+      <c r="P41">
+        <v>-1.421050008</v>
+      </c>
+      <c r="Q41">
+        <v>-0.8030500080000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1254365068618496</v>
+      </c>
+      <c r="T41">
+        <v>0.8924525176737845</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.05564195634836091</v>
+      </c>
+      <c r="W41">
+        <v>0.2255127008240114</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3477622271772557</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1664662225070927</v>
+      </c>
+      <c r="C42">
+        <v>1.127097313755174</v>
+      </c>
+      <c r="D42">
+        <v>12.25609731375518</v>
+      </c>
+      <c r="E42">
+        <v>8.290000000000001</v>
+      </c>
+      <c r="F42">
+        <v>11.14</v>
+      </c>
+      <c r="G42">
+        <v>0.011</v>
+      </c>
+      <c r="H42">
+        <v>25</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.52</v>
+      </c>
+      <c r="K42">
+        <v>0.618</v>
+      </c>
+      <c r="L42">
+        <v>0.902</v>
+      </c>
+      <c r="M42">
+        <v>2.660232</v>
+      </c>
+      <c r="N42">
+        <v>-1.758232</v>
+      </c>
+      <c r="O42">
+        <v>-0.28131712</v>
+      </c>
+      <c r="P42">
+        <v>-1.47691488</v>
+      </c>
+      <c r="Q42">
+        <v>-0.85891488</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1268804486428804</v>
+      </c>
+      <c r="T42">
+        <v>0.9073267263016809</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.05425090743965189</v>
+      </c>
+      <c r="W42">
+        <v>0.2258448833034112</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3390681714978243</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1684662225070927</v>
+      </c>
+      <c r="C43">
+        <v>0.6595566048213559</v>
+      </c>
+      <c r="D43">
+        <v>12.06705660482136</v>
+      </c>
+      <c r="E43">
+        <v>8.568500000000002</v>
+      </c>
+      <c r="F43">
+        <v>11.4185</v>
+      </c>
+      <c r="G43">
+        <v>0.011</v>
+      </c>
+      <c r="H43">
+        <v>25</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.52</v>
+      </c>
+      <c r="K43">
+        <v>0.618</v>
+      </c>
+      <c r="L43">
+        <v>0.902</v>
+      </c>
+      <c r="M43">
+        <v>2.7267378</v>
+      </c>
+      <c r="N43">
+        <v>-1.8247378</v>
+      </c>
+      <c r="O43">
+        <v>-0.2919580480000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.532779752</v>
+      </c>
+      <c r="Q43">
+        <v>-0.9147797520000002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1283733376029293</v>
+      </c>
+      <c r="T43">
+        <v>0.92270514539154</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.05292771457527013</v>
+      </c>
+      <c r="W43">
+        <v>0.2261608617594255</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3307982160954382</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1704662225070927</v>
+      </c>
+      <c r="C44">
+        <v>0.1977589241398725</v>
+      </c>
+      <c r="D44">
+        <v>11.88375892413987</v>
+      </c>
+      <c r="E44">
+        <v>8.847000000000001</v>
+      </c>
+      <c r="F44">
+        <v>11.697</v>
+      </c>
+      <c r="G44">
+        <v>0.011</v>
+      </c>
+      <c r="H44">
+        <v>25</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.52</v>
+      </c>
+      <c r="K44">
+        <v>0.618</v>
+      </c>
+      <c r="L44">
+        <v>0.902</v>
+      </c>
+      <c r="M44">
+        <v>2.7932436</v>
+      </c>
+      <c r="N44">
+        <v>-1.8912436</v>
+      </c>
+      <c r="O44">
+        <v>-0.3025989760000001</v>
+      </c>
+      <c r="P44">
+        <v>-1.588644624</v>
+      </c>
+      <c r="Q44">
+        <v>-0.9706446240000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1299177054926349</v>
+      </c>
+      <c r="T44">
+        <v>0.9386138547948423</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05166753089490655</v>
+      </c>
+      <c r="W44">
+        <v>0.2264617936222963</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3229220680931659</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1724662225070927</v>
+      </c>
+      <c r="C45">
+        <v>-0.2585535209377809</v>
+      </c>
+      <c r="D45">
+        <v>11.70594647906222</v>
+      </c>
+      <c r="E45">
+        <v>9.125500000000001</v>
+      </c>
+      <c r="F45">
+        <v>11.9755</v>
+      </c>
+      <c r="G45">
+        <v>0.011</v>
+      </c>
+      <c r="H45">
+        <v>25</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.52</v>
+      </c>
+      <c r="K45">
+        <v>0.618</v>
+      </c>
+      <c r="L45">
+        <v>0.902</v>
+      </c>
+      <c r="M45">
+        <v>2.8597494</v>
+      </c>
+      <c r="N45">
+        <v>-1.9577494</v>
+      </c>
+      <c r="O45">
+        <v>-0.3132399040000001</v>
+      </c>
+      <c r="P45">
+        <v>-1.644509496</v>
+      </c>
+      <c r="Q45">
+        <v>-1.026509496</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1315162617293478</v>
+      </c>
+      <c r="T45">
+        <v>0.9550807645280852</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05046596040897851</v>
+      </c>
+      <c r="W45">
+        <v>0.2267487286543359</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3154122525561156</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1744662225070927</v>
+      </c>
+      <c r="C46">
+        <v>-0.7096233214782259</v>
+      </c>
+      <c r="D46">
+        <v>11.53337667852178</v>
+      </c>
+      <c r="E46">
+        <v>9.404000000000002</v>
+      </c>
+      <c r="F46">
+        <v>12.254</v>
+      </c>
+      <c r="G46">
+        <v>0.011</v>
+      </c>
+      <c r="H46">
+        <v>25</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.52</v>
+      </c>
+      <c r="K46">
+        <v>0.618</v>
+      </c>
+      <c r="L46">
+        <v>0.902</v>
+      </c>
+      <c r="M46">
+        <v>2.9262552</v>
+      </c>
+      <c r="N46">
+        <v>-2.0242552</v>
+      </c>
+      <c r="O46">
+        <v>-0.3238808320000001</v>
+      </c>
+      <c r="P46">
+        <v>-1.700374368</v>
+      </c>
+      <c r="Q46">
+        <v>-1.082374368</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.133171909260229</v>
+      </c>
+      <c r="T46">
+        <v>0.9721357781803726</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.04931900676331989</v>
+      </c>
+      <c r="W46">
+        <v>0.2270226211849192</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3082437922707493</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1764662225070927</v>
+      </c>
+      <c r="C47">
+        <v>-1.15567897120091</v>
+      </c>
+      <c r="D47">
+        <v>11.36582102879909</v>
+      </c>
+      <c r="E47">
+        <v>9.682500000000001</v>
+      </c>
+      <c r="F47">
+        <v>12.5325</v>
+      </c>
+      <c r="G47">
+        <v>0.011</v>
+      </c>
+      <c r="H47">
+        <v>25</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.52</v>
+      </c>
+      <c r="K47">
+        <v>0.618</v>
+      </c>
+      <c r="L47">
+        <v>0.902</v>
+      </c>
+      <c r="M47">
+        <v>2.992761</v>
+      </c>
+      <c r="N47">
+        <v>-2.090761</v>
+      </c>
+      <c r="O47">
+        <v>-0.3345217600000001</v>
+      </c>
+      <c r="P47">
+        <v>-1.75623924</v>
+      </c>
+      <c r="Q47">
+        <v>-1.13823924</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1348877621558696</v>
+      </c>
+      <c r="T47">
+        <v>0.9898109741472881</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.04822302883524612</v>
+      </c>
+      <c r="W47">
+        <v>0.2272843407141432</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3013939302202883</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1784662225070927</v>
+      </c>
+      <c r="C48">
+        <v>-1.596935875837923</v>
+      </c>
+      <c r="D48">
+        <v>11.20306412416208</v>
+      </c>
+      <c r="E48">
+        <v>9.961000000000002</v>
+      </c>
+      <c r="F48">
+        <v>12.811</v>
+      </c>
+      <c r="G48">
+        <v>0.011</v>
+      </c>
+      <c r="H48">
+        <v>25</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.52</v>
+      </c>
+      <c r="K48">
+        <v>0.618</v>
+      </c>
+      <c r="L48">
+        <v>0.902</v>
+      </c>
+      <c r="M48">
+        <v>3.059266800000001</v>
+      </c>
+      <c r="N48">
+        <v>-2.1572668</v>
+      </c>
+      <c r="O48">
+        <v>-0.3451626880000001</v>
+      </c>
+      <c r="P48">
+        <v>-1.812104112</v>
+      </c>
+      <c r="Q48">
+        <v>-1.194104112</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.136667165158756</v>
+      </c>
+      <c r="T48">
+        <v>1.008140807001868</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.04717470212143642</v>
+      </c>
+      <c r="W48">
+        <v>0.227534681133401</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2948418882589776</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1804662225070927</v>
+      </c>
+      <c r="C49">
+        <v>-2.033597276994801</v>
+      </c>
+      <c r="D49">
+        <v>11.0449027230052</v>
+      </c>
+      <c r="E49">
+        <v>10.2395</v>
+      </c>
+      <c r="F49">
+        <v>13.0895</v>
+      </c>
+      <c r="G49">
+        <v>0.011</v>
+      </c>
+      <c r="H49">
+        <v>25</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.52</v>
+      </c>
+      <c r="K49">
+        <v>0.618</v>
+      </c>
+      <c r="L49">
+        <v>0.902</v>
+      </c>
+      <c r="M49">
+        <v>3.1257726</v>
+      </c>
+      <c r="N49">
+        <v>-2.2237726</v>
+      </c>
+      <c r="O49">
+        <v>-0.3558036160000001</v>
+      </c>
+      <c r="P49">
+        <v>-1.867968984</v>
+      </c>
+      <c r="Q49">
+        <v>-1.249968984</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1385137154447703</v>
+      </c>
+      <c r="T49">
+        <v>1.02716233166228</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04617098505502289</v>
+      </c>
+      <c r="W49">
+        <v>0.2277743687688605</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.288568656593893</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1824662225070927</v>
+      </c>
+      <c r="C50">
+        <v>-2.465855098844118</v>
+      </c>
+      <c r="D50">
+        <v>10.89114490115588</v>
+      </c>
+      <c r="E50">
+        <v>10.518</v>
+      </c>
+      <c r="F50">
+        <v>13.368</v>
+      </c>
+      <c r="G50">
+        <v>0.011</v>
+      </c>
+      <c r="H50">
+        <v>25</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.52</v>
+      </c>
+      <c r="K50">
+        <v>0.618</v>
+      </c>
+      <c r="L50">
+        <v>0.902</v>
+      </c>
+      <c r="M50">
+        <v>3.1922784</v>
+      </c>
+      <c r="N50">
+        <v>-2.2902784</v>
+      </c>
+      <c r="O50">
+        <v>-0.3664445440000001</v>
+      </c>
+      <c r="P50">
+        <v>-1.923833856</v>
+      </c>
+      <c r="Q50">
+        <v>-1.305833856</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1404312868956313</v>
+      </c>
+      <c r="T50">
+        <v>1.046915453425016</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.04520908953304324</v>
+      </c>
+      <c r="W50">
+        <v>0.2280040694195093</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2825568095815202</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1844662225070927</v>
+      </c>
+      <c r="C51">
+        <v>-2.893890725068317</v>
+      </c>
+      <c r="D51">
+        <v>10.74160927493168</v>
+      </c>
+      <c r="E51">
+        <v>10.7965</v>
+      </c>
+      <c r="F51">
+        <v>13.6465</v>
+      </c>
+      <c r="G51">
+        <v>0.011</v>
+      </c>
+      <c r="H51">
+        <v>25</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.52</v>
+      </c>
+      <c r="K51">
+        <v>0.618</v>
+      </c>
+      <c r="L51">
+        <v>0.902</v>
+      </c>
+      <c r="M51">
+        <v>3.2587842</v>
+      </c>
+      <c r="N51">
+        <v>-2.3567842</v>
+      </c>
+      <c r="O51">
+        <v>-0.377085472</v>
+      </c>
+      <c r="P51">
+        <v>-1.979698728</v>
+      </c>
+      <c r="Q51">
+        <v>-1.361698728</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1424240572269181</v>
+      </c>
+      <c r="T51">
+        <v>1.067443207413742</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04428645505277706</v>
+      </c>
+      <c r="W51">
+        <v>0.2282243945333969</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2767903440798566</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1864662225070927</v>
+      </c>
+      <c r="C52">
+        <v>-3.317875712664799</v>
+      </c>
+      <c r="D52">
+        <v>10.5961242873352</v>
+      </c>
+      <c r="E52">
+        <v>11.075</v>
+      </c>
+      <c r="F52">
+        <v>13.925</v>
+      </c>
+      <c r="G52">
+        <v>0.011</v>
+      </c>
+      <c r="H52">
+        <v>25</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.52</v>
+      </c>
+      <c r="K52">
+        <v>0.618</v>
+      </c>
+      <c r="L52">
+        <v>0.902</v>
+      </c>
+      <c r="M52">
+        <v>3.32529</v>
+      </c>
+      <c r="N52">
+        <v>-2.42329</v>
+      </c>
+      <c r="O52">
+        <v>-0.3877264000000001</v>
+      </c>
+      <c r="P52">
+        <v>-2.0355636</v>
+      </c>
+      <c r="Q52">
+        <v>-1.4175636</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1444965383714565</v>
+      </c>
+      <c r="T52">
+        <v>1.088792071562017</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.04340072595172151</v>
+      </c>
+      <c r="W52">
+        <v>0.2284359066427289</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2712545371982594</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1884662225070927</v>
+      </c>
+      <c r="C53">
+        <v>-3.737972448519253</v>
+      </c>
+      <c r="D53">
+        <v>10.45452755148075</v>
+      </c>
+      <c r="E53">
+        <v>11.3535</v>
+      </c>
+      <c r="F53">
+        <v>14.2035</v>
+      </c>
+      <c r="G53">
+        <v>0.011</v>
+      </c>
+      <c r="H53">
+        <v>25</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.52</v>
+      </c>
+      <c r="K53">
+        <v>0.618</v>
+      </c>
+      <c r="L53">
+        <v>0.902</v>
+      </c>
+      <c r="M53">
+        <v>3.391795800000001</v>
+      </c>
+      <c r="N53">
+        <v>-2.4897958</v>
+      </c>
+      <c r="O53">
+        <v>-0.3983673280000001</v>
+      </c>
+      <c r="P53">
+        <v>-2.091428472</v>
+      </c>
+      <c r="Q53">
+        <v>-1.473428472000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1466536105831189</v>
+      </c>
+      <c r="T53">
+        <v>1.111012317920426</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04254973132521716</v>
+      </c>
+      <c r="W53">
+        <v>0.2286391241595382</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2659358207826072</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1904662225070927</v>
+      </c>
+      <c r="C54">
+        <v>-4.154334754030181</v>
+      </c>
+      <c r="D54">
+        <v>10.31666524596982</v>
+      </c>
+      <c r="E54">
+        <v>11.632</v>
+      </c>
+      <c r="F54">
+        <v>14.482</v>
+      </c>
+      <c r="G54">
+        <v>0.011</v>
+      </c>
+      <c r="H54">
+        <v>25</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.52</v>
+      </c>
+      <c r="K54">
+        <v>0.618</v>
+      </c>
+      <c r="L54">
+        <v>0.902</v>
+      </c>
+      <c r="M54">
+        <v>3.4583016</v>
+      </c>
+      <c r="N54">
+        <v>-2.5563016</v>
+      </c>
+      <c r="O54">
+        <v>-0.4090082560000001</v>
+      </c>
+      <c r="P54">
+        <v>-2.147293344</v>
+      </c>
+      <c r="Q54">
+        <v>-1.529293344</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1489005608036005</v>
+      </c>
+      <c r="T54">
+        <v>1.134158407877101</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04173146726127068</v>
+      </c>
+      <c r="W54">
+        <v>0.2288345256180086</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2608216703829417</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1924662225070927</v>
+      </c>
+      <c r="C55">
+        <v>-4.567108442517496</v>
+      </c>
+      <c r="D55">
+        <v>10.18239155748251</v>
+      </c>
+      <c r="E55">
+        <v>11.9105</v>
+      </c>
+      <c r="F55">
+        <v>14.7605</v>
+      </c>
+      <c r="G55">
+        <v>0.011</v>
+      </c>
+      <c r="H55">
+        <v>25</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.52</v>
+      </c>
+      <c r="K55">
+        <v>0.618</v>
+      </c>
+      <c r="L55">
+        <v>0.902</v>
+      </c>
+      <c r="M55">
+        <v>3.524807400000001</v>
+      </c>
+      <c r="N55">
+        <v>-2.622807400000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.4196491840000002</v>
+      </c>
+      <c r="P55">
+        <v>-2.203158216</v>
+      </c>
+      <c r="Q55">
+        <v>-1.585158216</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1512431259270814</v>
+      </c>
+      <c r="T55">
+        <v>1.158289437831933</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04094408108652972</v>
+      </c>
+      <c r="W55">
+        <v>0.2290225534365367</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2559005067908108</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1944662225070927</v>
+      </c>
+      <c r="C56">
+        <v>-4.976431833661564</v>
+      </c>
+      <c r="D56">
+        <v>10.05156816633844</v>
+      </c>
+      <c r="E56">
+        <v>12.189</v>
+      </c>
+      <c r="F56">
+        <v>15.039</v>
+      </c>
+      <c r="G56">
+        <v>0.011</v>
+      </c>
+      <c r="H56">
+        <v>25</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.52</v>
+      </c>
+      <c r="K56">
+        <v>0.618</v>
+      </c>
+      <c r="L56">
+        <v>0.902</v>
+      </c>
+      <c r="M56">
+        <v>3.591313200000001</v>
+      </c>
+      <c r="N56">
+        <v>-2.6893132</v>
+      </c>
+      <c r="O56">
+        <v>-0.4302901120000002</v>
+      </c>
+      <c r="P56">
+        <v>-2.259023088</v>
+      </c>
+      <c r="Q56">
+        <v>-1.641023088</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1536875417081049</v>
+      </c>
+      <c r="T56">
+        <v>1.183469643002193</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0401858573627051</v>
+      </c>
+      <c r="W56">
+        <v>0.229203617261786</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2511616085169068</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1964662225070927</v>
+      </c>
+      <c r="C57">
+        <v>-5.382436228788256</v>
+      </c>
+      <c r="D57">
+        <v>9.924063771211747</v>
+      </c>
+      <c r="E57">
+        <v>12.4675</v>
+      </c>
+      <c r="F57">
+        <v>15.3175</v>
+      </c>
+      <c r="G57">
+        <v>0.011</v>
+      </c>
+      <c r="H57">
+        <v>25</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.52</v>
+      </c>
+      <c r="K57">
+        <v>0.618</v>
+      </c>
+      <c r="L57">
+        <v>0.902</v>
+      </c>
+      <c r="M57">
+        <v>3.657819000000001</v>
+      </c>
+      <c r="N57">
+        <v>-2.755819000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.4409310400000002</v>
+      </c>
+      <c r="P57">
+        <v>-2.314887960000001</v>
+      </c>
+      <c r="Q57">
+        <v>-1.696887960000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1562405981905073</v>
+      </c>
+      <c r="T57">
+        <v>1.209768968402241</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03945520541065591</v>
+      </c>
+      <c r="W57">
+        <v>0.2293780969479354</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2465950338165994</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1984662225070927</v>
+      </c>
+      <c r="C58">
+        <v>-5.785246350433063</v>
+      </c>
+      <c r="D58">
+        <v>9.79975364956694</v>
+      </c>
+      <c r="E58">
+        <v>12.746</v>
+      </c>
+      <c r="F58">
+        <v>15.596</v>
+      </c>
+      <c r="G58">
+        <v>0.011</v>
+      </c>
+      <c r="H58">
+        <v>25</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.52</v>
+      </c>
+      <c r="K58">
+        <v>0.618</v>
+      </c>
+      <c r="L58">
+        <v>0.902</v>
+      </c>
+      <c r="M58">
+        <v>3.724324800000001</v>
+      </c>
+      <c r="N58">
+        <v>-2.822324800000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.4515719680000002</v>
+      </c>
+      <c r="P58">
+        <v>-2.370752832</v>
+      </c>
+      <c r="Q58">
+        <v>-1.752752832000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.158909702694837</v>
+      </c>
+      <c r="T58">
+        <v>1.237263717684111</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03875064817117992</v>
+      </c>
+      <c r="W58">
+        <v>0.2295463452167223</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2421915510698744</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2004662225070927</v>
+      </c>
+      <c r="C59">
+        <v>-6.18498074927772</v>
+      </c>
+      <c r="D59">
+        <v>9.678519250722283</v>
+      </c>
+      <c r="E59">
+        <v>13.0245</v>
+      </c>
+      <c r="F59">
+        <v>15.8745</v>
+      </c>
+      <c r="G59">
+        <v>0.011</v>
+      </c>
+      <c r="H59">
+        <v>25</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.52</v>
+      </c>
+      <c r="K59">
+        <v>0.618</v>
+      </c>
+      <c r="L59">
+        <v>0.902</v>
+      </c>
+      <c r="M59">
+        <v>3.790830600000001</v>
+      </c>
+      <c r="N59">
+        <v>-2.888830600000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.4622128960000002</v>
+      </c>
+      <c r="P59">
+        <v>-2.426617704000001</v>
+      </c>
+      <c r="Q59">
+        <v>-1.808617704000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1617029515947169</v>
+      </c>
+      <c r="T59">
+        <v>1.266037292513974</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.03807081223835219</v>
+      </c>
+      <c r="W59">
+        <v>0.2297086900374815</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2379425764897012</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2024662225070927</v>
+      </c>
+      <c r="C60">
+        <v>-6.58175218125022</v>
+      </c>
+      <c r="D60">
+        <v>9.560247818749779</v>
+      </c>
+      <c r="E60">
+        <v>13.303</v>
+      </c>
+      <c r="F60">
+        <v>16.153</v>
+      </c>
+      <c r="G60">
+        <v>0.011</v>
+      </c>
+      <c r="H60">
+        <v>25</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.52</v>
+      </c>
+      <c r="K60">
+        <v>0.618</v>
+      </c>
+      <c r="L60">
+        <v>0.902</v>
+      </c>
+      <c r="M60">
+        <v>3.8573364</v>
+      </c>
+      <c r="N60">
+        <v>-2.9553364</v>
+      </c>
+      <c r="O60">
+        <v>-0.472853824</v>
+      </c>
+      <c r="P60">
+        <v>-2.482482576</v>
+      </c>
+      <c r="Q60">
+        <v>-1.864482576</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.164629212346972</v>
+      </c>
+      <c r="T60">
+        <v>1.29618103757383</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03741441892389786</v>
+      </c>
+      <c r="W60">
+        <v>0.2298654367609732</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2338401182743616</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2044662225070927</v>
+      </c>
+      <c r="C61">
+        <v>-6.975667957309705</v>
+      </c>
+      <c r="D61">
+        <v>9.444832042690296</v>
+      </c>
+      <c r="E61">
+        <v>13.5815</v>
+      </c>
+      <c r="F61">
+        <v>16.4315</v>
+      </c>
+      <c r="G61">
+        <v>0.011</v>
+      </c>
+      <c r="H61">
+        <v>25</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.52</v>
+      </c>
+      <c r="K61">
+        <v>0.618</v>
+      </c>
+      <c r="L61">
+        <v>0.902</v>
+      </c>
+      <c r="M61">
+        <v>3.9238422</v>
+      </c>
+      <c r="N61">
+        <v>-3.0218422</v>
+      </c>
+      <c r="O61">
+        <v>-0.4834947520000001</v>
+      </c>
+      <c r="P61">
+        <v>-2.538347448</v>
+      </c>
+      <c r="Q61">
+        <v>-1.920347448</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1676982175261665</v>
+      </c>
+      <c r="T61">
+        <v>1.327795209221972</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03678027623027247</v>
+      </c>
+      <c r="W61">
+        <v>0.2300168700362109</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2298767264392029</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2064662225070927</v>
+      </c>
+      <c r="C62">
+        <v>-7.366830268196933</v>
+      </c>
+      <c r="D62">
+        <v>9.332169731803068</v>
+      </c>
+      <c r="E62">
+        <v>13.86</v>
+      </c>
+      <c r="F62">
+        <v>16.71</v>
+      </c>
+      <c r="G62">
+        <v>0.011</v>
+      </c>
+      <c r="H62">
+        <v>25</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.52</v>
+      </c>
+      <c r="K62">
+        <v>0.618</v>
+      </c>
+      <c r="L62">
+        <v>0.902</v>
+      </c>
+      <c r="M62">
+        <v>3.990348</v>
+      </c>
+      <c r="N62">
+        <v>-3.088348</v>
+      </c>
+      <c r="O62">
+        <v>-0.4941356800000001</v>
+      </c>
+      <c r="P62">
+        <v>-2.59421232</v>
+      </c>
+      <c r="Q62">
+        <v>-1.97621232</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1709206729643206</v>
+      </c>
+      <c r="T62">
+        <v>1.360990089452521</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03616727162643459</v>
+      </c>
+      <c r="W62">
+        <v>0.2301632555356074</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2260454476652162</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2084662225070927</v>
+      </c>
+      <c r="C63">
+        <v>-7.755336486216116</v>
+      </c>
+      <c r="D63">
+        <v>9.222163513783887</v>
+      </c>
+      <c r="E63">
+        <v>14.1385</v>
+      </c>
+      <c r="F63">
+        <v>16.9885</v>
+      </c>
+      <c r="G63">
+        <v>0.011</v>
+      </c>
+      <c r="H63">
+        <v>25</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.52</v>
+      </c>
+      <c r="K63">
+        <v>0.618</v>
+      </c>
+      <c r="L63">
+        <v>0.902</v>
+      </c>
+      <c r="M63">
+        <v>4.056853800000001</v>
+      </c>
+      <c r="N63">
+        <v>-3.154853800000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.5047766080000002</v>
+      </c>
+      <c r="P63">
+        <v>-2.650077192</v>
+      </c>
+      <c r="Q63">
+        <v>-2.032077192</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1743083825275084</v>
+      </c>
+      <c r="T63">
+        <v>1.395887271233355</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03557436553419795</v>
+      </c>
+      <c r="W63">
+        <v>0.2303048415104335</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2223397845887372</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2104662225070927</v>
+      </c>
+      <c r="C64">
+        <v>-8.141279445921278</v>
+      </c>
+      <c r="D64">
+        <v>9.114720554078723</v>
+      </c>
+      <c r="E64">
+        <v>14.417</v>
+      </c>
+      <c r="F64">
+        <v>17.267</v>
+      </c>
+      <c r="G64">
+        <v>0.011</v>
+      </c>
+      <c r="H64">
+        <v>25</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.52</v>
+      </c>
+      <c r="K64">
+        <v>0.618</v>
+      </c>
+      <c r="L64">
+        <v>0.902</v>
+      </c>
+      <c r="M64">
+        <v>4.1233596</v>
+      </c>
+      <c r="N64">
+        <v>-3.2213596</v>
+      </c>
+      <c r="O64">
+        <v>-0.5154175360000001</v>
+      </c>
+      <c r="P64">
+        <v>-2.705942063999999</v>
+      </c>
+      <c r="Q64">
+        <v>-2.087942063999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1778743925940217</v>
+      </c>
+      <c r="T64">
+        <v>1.432621146792128</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03500058544493671</v>
+      </c>
+      <c r="W64">
+        <v>0.2304418601957491</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2187536590308544</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2124662225070927</v>
+      </c>
+      <c r="C65">
+        <v>-8.524747705407737</v>
+      </c>
+      <c r="D65">
+        <v>9.009752294592264</v>
+      </c>
+      <c r="E65">
+        <v>14.6955</v>
+      </c>
+      <c r="F65">
+        <v>17.5455</v>
+      </c>
+      <c r="G65">
+        <v>0.011</v>
+      </c>
+      <c r="H65">
+        <v>25</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.52</v>
+      </c>
+      <c r="K65">
+        <v>0.618</v>
+      </c>
+      <c r="L65">
+        <v>0.902</v>
+      </c>
+      <c r="M65">
+        <v>4.1898654</v>
+      </c>
+      <c r="N65">
+        <v>-3.2878654</v>
+      </c>
+      <c r="O65">
+        <v>-0.5260584640000001</v>
+      </c>
+      <c r="P65">
+        <v>-2.761806936</v>
+      </c>
+      <c r="Q65">
+        <v>-2.143806936</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1816331599614277</v>
+      </c>
+      <c r="T65">
+        <v>1.471340637245969</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03444502059660437</v>
+      </c>
+      <c r="W65">
+        <v>0.2305745290815309</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2152813787287773</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2144662225070927</v>
+      </c>
+      <c r="C66">
+        <v>-8.90582578975436</v>
+      </c>
+      <c r="D66">
+        <v>8.907174210245643</v>
+      </c>
+      <c r="E66">
+        <v>14.974</v>
+      </c>
+      <c r="F66">
+        <v>17.824</v>
+      </c>
+      <c r="G66">
+        <v>0.011</v>
+      </c>
+      <c r="H66">
+        <v>25</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.52</v>
+      </c>
+      <c r="K66">
+        <v>0.618</v>
+      </c>
+      <c r="L66">
+        <v>0.902</v>
+      </c>
+      <c r="M66">
+        <v>4.2563712</v>
+      </c>
+      <c r="N66">
+        <v>-3.3543712</v>
+      </c>
+      <c r="O66">
+        <v>-0.5366993920000002</v>
+      </c>
+      <c r="P66">
+        <v>-2.817671808</v>
+      </c>
+      <c r="Q66">
+        <v>-2.199671808</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1856007477381341</v>
+      </c>
+      <c r="T66">
+        <v>1.512211210502802</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03390681714978243</v>
+      </c>
+      <c r="W66">
+        <v>0.230703052064632</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2119176071861402</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2164662225070927</v>
+      </c>
+      <c r="C67">
+        <v>-9.284594418023193</v>
+      </c>
+      <c r="D67">
+        <v>8.80690558197681</v>
+      </c>
+      <c r="E67">
+        <v>15.2525</v>
+      </c>
+      <c r="F67">
+        <v>18.1025</v>
+      </c>
+      <c r="G67">
+        <v>0.011</v>
+      </c>
+      <c r="H67">
+        <v>25</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.52</v>
+      </c>
+      <c r="K67">
+        <v>0.618</v>
+      </c>
+      <c r="L67">
+        <v>0.902</v>
+      </c>
+      <c r="M67">
+        <v>4.322877000000001</v>
+      </c>
+      <c r="N67">
+        <v>-3.420877000000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.5473403200000002</v>
+      </c>
+      <c r="P67">
+        <v>-2.873536680000001</v>
+      </c>
+      <c r="Q67">
+        <v>-2.255536680000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1897950548163665</v>
+      </c>
+      <c r="T67">
+        <v>1.555417245088596</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03338517380901654</v>
+      </c>
+      <c r="W67">
+        <v>0.2308276204944069</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2086573363063534</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2184662225070927</v>
+      </c>
+      <c r="C68">
+        <v>-9.661130715097661</v>
+      </c>
+      <c r="D68">
+        <v>8.70886928490234</v>
+      </c>
+      <c r="E68">
+        <v>15.531</v>
+      </c>
+      <c r="F68">
+        <v>18.381</v>
+      </c>
+      <c r="G68">
+        <v>0.011</v>
+      </c>
+      <c r="H68">
+        <v>25</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.52</v>
+      </c>
+      <c r="K68">
+        <v>0.618</v>
+      </c>
+      <c r="L68">
+        <v>0.902</v>
+      </c>
+      <c r="M68">
+        <v>4.3893828</v>
+      </c>
+      <c r="N68">
+        <v>-3.4873828</v>
+      </c>
+      <c r="O68">
+        <v>-0.557981248</v>
+      </c>
+      <c r="P68">
+        <v>-2.929401552</v>
+      </c>
+      <c r="Q68">
+        <v>-2.311401552</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1942360858403772</v>
+      </c>
+      <c r="T68">
+        <v>1.601164811120614</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03287933784221327</v>
+      </c>
+      <c r="W68">
+        <v>0.2309484141232795</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2054958615138329</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2204662225070927</v>
+      </c>
+      <c r="C69">
+        <v>-10.03550840952776</v>
+      </c>
+      <c r="D69">
+        <v>8.612991590472246</v>
+      </c>
+      <c r="E69">
+        <v>15.8095</v>
+      </c>
+      <c r="F69">
+        <v>18.6595</v>
+      </c>
+      <c r="G69">
+        <v>0.011</v>
+      </c>
+      <c r="H69">
+        <v>25</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.52</v>
+      </c>
+      <c r="K69">
+        <v>0.618</v>
+      </c>
+      <c r="L69">
+        <v>0.902</v>
+      </c>
+      <c r="M69">
+        <v>4.455888600000001</v>
+      </c>
+      <c r="N69">
+        <v>-3.553888600000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.5686221760000002</v>
+      </c>
+      <c r="P69">
+        <v>-2.985266424</v>
+      </c>
+      <c r="Q69">
+        <v>-2.367266424</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1989462702597826</v>
+      </c>
+      <c r="T69">
+        <v>1.649684956912147</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03238860145650859</v>
+      </c>
+      <c r="W69">
+        <v>0.2310656019721858</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2024287591031787</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2224662225070927</v>
+      </c>
+      <c r="C70">
+        <v>-10.4077980184488</v>
+      </c>
+      <c r="D70">
+        <v>8.519201981551207</v>
+      </c>
+      <c r="E70">
+        <v>16.088</v>
+      </c>
+      <c r="F70">
+        <v>18.938</v>
+      </c>
+      <c r="G70">
+        <v>0.011</v>
+      </c>
+      <c r="H70">
+        <v>25</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.52</v>
+      </c>
+      <c r="K70">
+        <v>0.618</v>
+      </c>
+      <c r="L70">
+        <v>0.902</v>
+      </c>
+      <c r="M70">
+        <v>4.5223944</v>
+      </c>
+      <c r="N70">
+        <v>-3.6203944</v>
+      </c>
+      <c r="O70">
+        <v>-0.5792631040000001</v>
+      </c>
+      <c r="P70">
+        <v>-3.041131296</v>
+      </c>
+      <c r="Q70">
+        <v>-2.423131296</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2039508412054008</v>
+      </c>
+      <c r="T70">
+        <v>1.701237611815652</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03191229849391287</v>
+      </c>
+      <c r="W70">
+        <v>0.2311793431196536</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1994518655869555</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2244662225070927</v>
+      </c>
+      <c r="C71">
+        <v>-10.77806702054853</v>
+      </c>
+      <c r="D71">
+        <v>8.427432979451476</v>
+      </c>
+      <c r="E71">
+        <v>16.3665</v>
+      </c>
+      <c r="F71">
+        <v>19.2165</v>
+      </c>
+      <c r="G71">
+        <v>0.011</v>
+      </c>
+      <c r="H71">
+        <v>25</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.52</v>
+      </c>
+      <c r="K71">
+        <v>0.618</v>
+      </c>
+      <c r="L71">
+        <v>0.902</v>
+      </c>
+      <c r="M71">
+        <v>4.588900200000001</v>
+      </c>
+      <c r="N71">
+        <v>-3.686900200000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.5899040320000003</v>
+      </c>
+      <c r="P71">
+        <v>-3.096996168000001</v>
+      </c>
+      <c r="Q71">
+        <v>-2.478996168000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2092782876958977</v>
+      </c>
+      <c r="T71">
+        <v>1.756116244454867</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03144980141429094</v>
+      </c>
+      <c r="W71">
+        <v>0.2312897874222673</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1965612588393184</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2264662225070927</v>
+      </c>
+      <c r="C72">
+        <v>-11.14638001797414</v>
+      </c>
+      <c r="D72">
+        <v>8.337619982025869</v>
+      </c>
+      <c r="E72">
+        <v>16.645</v>
+      </c>
+      <c r="F72">
+        <v>19.495</v>
+      </c>
+      <c r="G72">
+        <v>0.011</v>
+      </c>
+      <c r="H72">
+        <v>25</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.52</v>
+      </c>
+      <c r="K72">
+        <v>0.618</v>
+      </c>
+      <c r="L72">
+        <v>0.902</v>
+      </c>
+      <c r="M72">
+        <v>4.655406000000001</v>
+      </c>
+      <c r="N72">
+        <v>-3.753406000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.6005449600000002</v>
+      </c>
+      <c r="P72">
+        <v>-3.152861040000001</v>
+      </c>
+      <c r="Q72">
+        <v>-2.534861040000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2149608972857609</v>
+      </c>
+      <c r="T72">
+        <v>1.814653452603362</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03100051853694393</v>
+      </c>
+      <c r="W72">
+        <v>0.2313970761733778</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1937532408558995</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2284662225070928</v>
+      </c>
+      <c r="C73">
+        <v>-11.51279888799553</v>
+      </c>
+      <c r="D73">
+        <v>8.249701112004464</v>
+      </c>
+      <c r="E73">
+        <v>16.9235</v>
+      </c>
+      <c r="F73">
+        <v>19.7735</v>
+      </c>
+      <c r="G73">
+        <v>0.011</v>
+      </c>
+      <c r="H73">
+        <v>25</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.52</v>
+      </c>
+      <c r="K73">
+        <v>0.618</v>
+      </c>
+      <c r="L73">
+        <v>0.902</v>
+      </c>
+      <c r="M73">
+        <v>4.7219118</v>
+      </c>
+      <c r="N73">
+        <v>-3.8199118</v>
+      </c>
+      <c r="O73">
+        <v>-0.6111858880000001</v>
+      </c>
+      <c r="P73">
+        <v>-3.208725912</v>
+      </c>
+      <c r="Q73">
+        <v>-2.590725912</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2210354109852699</v>
+      </c>
+      <c r="T73">
+        <v>1.877227709589685</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03056389151529684</v>
+      </c>
+      <c r="W73">
+        <v>0.2315013427061471</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1910243219706053</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2304662225070927</v>
+      </c>
+      <c r="C74">
+        <v>-11.87738292517323</v>
+      </c>
+      <c r="D74">
+        <v>8.163617074826773</v>
+      </c>
+      <c r="E74">
+        <v>17.202</v>
+      </c>
+      <c r="F74">
+        <v>20.052</v>
+      </c>
+      <c r="G74">
+        <v>0.011</v>
+      </c>
+      <c r="H74">
+        <v>25</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.52</v>
+      </c>
+      <c r="K74">
+        <v>0.618</v>
+      </c>
+      <c r="L74">
+        <v>0.902</v>
+      </c>
+      <c r="M74">
+        <v>4.7884176</v>
+      </c>
+      <c r="N74">
+        <v>-3.8864176</v>
+      </c>
+      <c r="O74">
+        <v>-0.6218268160000001</v>
+      </c>
+      <c r="P74">
+        <v>-3.264590784</v>
+      </c>
+      <c r="Q74">
+        <v>-2.646590784</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.227543818520458</v>
+      </c>
+      <c r="T74">
+        <v>1.944271556360745</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03013939302202883</v>
+      </c>
+      <c r="W74">
+        <v>0.2316027129463395</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1883712063876801</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2324662225070927</v>
+      </c>
+      <c r="C75">
+        <v>-12.24018897471708</v>
+      </c>
+      <c r="D75">
+        <v>8.079311025282919</v>
+      </c>
+      <c r="E75">
+        <v>17.4805</v>
+      </c>
+      <c r="F75">
+        <v>20.3305</v>
+      </c>
+      <c r="G75">
+        <v>0.011</v>
+      </c>
+      <c r="H75">
+        <v>25</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.52</v>
+      </c>
+      <c r="K75">
+        <v>0.618</v>
+      </c>
+      <c r="L75">
+        <v>0.902</v>
+      </c>
+      <c r="M75">
+        <v>4.854923400000001</v>
+      </c>
+      <c r="N75">
+        <v>-3.9529234</v>
+      </c>
+      <c r="O75">
+        <v>-0.6324677440000002</v>
+      </c>
+      <c r="P75">
+        <v>-3.320455656</v>
+      </c>
+      <c r="Q75">
+        <v>-2.702455656</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2345343303175121</v>
+      </c>
+      <c r="T75">
+        <v>2.016281614003735</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02972652462446678</v>
+      </c>
+      <c r="W75">
+        <v>0.2317013059196773</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1857907789029174</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2344662225070927</v>
+      </c>
+      <c r="C76">
+        <v>-12.60127155766637</v>
+      </c>
+      <c r="D76">
+        <v>7.996728442333631</v>
+      </c>
+      <c r="E76">
+        <v>17.759</v>
+      </c>
+      <c r="F76">
+        <v>20.609</v>
+      </c>
+      <c r="G76">
+        <v>0.011</v>
+      </c>
+      <c r="H76">
+        <v>25</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.52</v>
+      </c>
+      <c r="K76">
+        <v>0.618</v>
+      </c>
+      <c r="L76">
+        <v>0.902</v>
+      </c>
+      <c r="M76">
+        <v>4.9214292</v>
+      </c>
+      <c r="N76">
+        <v>-4.0194292</v>
+      </c>
+      <c r="O76">
+        <v>-0.6431086720000002</v>
+      </c>
+      <c r="P76">
+        <v>-3.376320528</v>
+      </c>
+      <c r="Q76">
+        <v>-2.758320528</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2420625737912625</v>
+      </c>
+      <c r="T76">
+        <v>2.093830906850032</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02932481483224426</v>
+      </c>
+      <c r="W76">
+        <v>0.2317972342180601</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1832800927015267</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2364662225070927</v>
+      </c>
+      <c r="C77">
+        <v>-12.96068298847036</v>
+      </c>
+      <c r="D77">
+        <v>7.915817011529646</v>
+      </c>
+      <c r="E77">
+        <v>18.0375</v>
+      </c>
+      <c r="F77">
+        <v>20.8875</v>
+      </c>
+      <c r="G77">
+        <v>0.011</v>
+      </c>
+      <c r="H77">
+        <v>25</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.52</v>
+      </c>
+      <c r="K77">
+        <v>0.618</v>
+      </c>
+      <c r="L77">
+        <v>0.902</v>
+      </c>
+      <c r="M77">
+        <v>4.987935000000001</v>
+      </c>
+      <c r="N77">
+        <v>-4.085935000000001</v>
+      </c>
+      <c r="O77">
+        <v>-0.6537496000000003</v>
+      </c>
+      <c r="P77">
+        <v>-3.432185400000001</v>
+      </c>
+      <c r="Q77">
+        <v>-2.814185400000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.250193076742913</v>
+      </c>
+      <c r="T77">
+        <v>2.177584143124034</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02893381730114767</v>
+      </c>
+      <c r="W77">
+        <v>0.231890604428486</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1808363581321729</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2384662225070928</v>
+      </c>
+      <c r="C78">
+        <v>-13.3184734855022</v>
+      </c>
+      <c r="D78">
+        <v>7.836526514497797</v>
+      </c>
+      <c r="E78">
+        <v>18.316</v>
+      </c>
+      <c r="F78">
+        <v>21.166</v>
+      </c>
+      <c r="G78">
+        <v>0.011</v>
+      </c>
+      <c r="H78">
+        <v>25</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.52</v>
+      </c>
+      <c r="K78">
+        <v>0.618</v>
+      </c>
+      <c r="L78">
+        <v>0.902</v>
+      </c>
+      <c r="M78">
+        <v>5.0544408</v>
+      </c>
+      <c r="N78">
+        <v>-4.1524408</v>
+      </c>
+      <c r="O78">
+        <v>-0.6643905280000001</v>
+      </c>
+      <c r="P78">
+        <v>-3.488050272</v>
+      </c>
+      <c r="Q78">
+        <v>-2.870050272</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2590011216072011</v>
+      </c>
+      <c r="T78">
+        <v>2.268316815754202</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02855310917876415</v>
+      </c>
+      <c r="W78">
+        <v>0.2319815175281111</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.178456932367276</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2404662225070927</v>
+      </c>
+      <c r="C79">
+        <v>-13.67469127499689</v>
+      </c>
+      <c r="D79">
+        <v>7.758808725003109</v>
+      </c>
+      <c r="E79">
+        <v>18.5945</v>
+      </c>
+      <c r="F79">
+        <v>21.4445</v>
+      </c>
+      <c r="G79">
+        <v>0.011</v>
+      </c>
+      <c r="H79">
+        <v>25</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.52</v>
+      </c>
+      <c r="K79">
+        <v>0.618</v>
+      </c>
+      <c r="L79">
+        <v>0.902</v>
+      </c>
+      <c r="M79">
+        <v>5.120946600000001</v>
+      </c>
+      <c r="N79">
+        <v>-4.218946600000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.6750314560000003</v>
+      </c>
+      <c r="P79">
+        <v>-3.543915144000001</v>
+      </c>
+      <c r="Q79">
+        <v>-2.925915144000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2685750834162098</v>
+      </c>
+      <c r="T79">
+        <v>2.366939286004385</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02818228957903994</v>
+      </c>
+      <c r="W79">
+        <v>0.2320700692485253</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1761393098689996</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2424662225070927</v>
+      </c>
+      <c r="C80">
+        <v>-14.02938268886507</v>
+      </c>
+      <c r="D80">
+        <v>7.682617311134931</v>
+      </c>
+      <c r="E80">
+        <v>18.873</v>
+      </c>
+      <c r="F80">
+        <v>21.723</v>
+      </c>
+      <c r="G80">
+        <v>0.011</v>
+      </c>
+      <c r="H80">
+        <v>25</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.52</v>
+      </c>
+      <c r="K80">
+        <v>0.618</v>
+      </c>
+      <c r="L80">
+        <v>0.902</v>
+      </c>
+      <c r="M80">
+        <v>5.187452400000001</v>
+      </c>
+      <c r="N80">
+        <v>-4.2854524</v>
+      </c>
+      <c r="O80">
+        <v>-0.6856723840000002</v>
+      </c>
+      <c r="P80">
+        <v>-3.599780016</v>
+      </c>
+      <c r="Q80">
+        <v>-2.981780016000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.279019405389674</v>
+      </c>
+      <c r="T80">
+        <v>2.474527435368221</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02782097817418045</v>
+      </c>
+      <c r="W80">
+        <v>0.2321563504120057</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1738811135886278</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2444662225070927</v>
+      </c>
+      <c r="C81">
+        <v>-14.38259225679979</v>
+      </c>
+      <c r="D81">
+        <v>7.607907743200216</v>
+      </c>
+      <c r="E81">
+        <v>19.1515</v>
+      </c>
+      <c r="F81">
+        <v>22.0015</v>
+      </c>
+      <c r="G81">
+        <v>0.011</v>
+      </c>
+      <c r="H81">
+        <v>25</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.52</v>
+      </c>
+      <c r="K81">
+        <v>0.618</v>
+      </c>
+      <c r="L81">
+        <v>0.902</v>
+      </c>
+      <c r="M81">
+        <v>5.253958200000001</v>
+      </c>
+      <c r="N81">
+        <v>-4.351958200000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.6963133120000004</v>
+      </c>
+      <c r="P81">
+        <v>-3.655644888000001</v>
+      </c>
+      <c r="Q81">
+        <v>-3.037644888000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2904584246939441</v>
+      </c>
+      <c r="T81">
+        <v>2.59236207514766</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02746881389349462</v>
+      </c>
+      <c r="W81">
+        <v>0.2322404472422335</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1716800868343413</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2464662225070927</v>
+      </c>
+      <c r="C82">
+        <v>-14.73436279306083</v>
+      </c>
+      <c r="D82">
+        <v>7.534637206939169</v>
+      </c>
+      <c r="E82">
+        <v>19.43</v>
+      </c>
+      <c r="F82">
+        <v>22.28</v>
+      </c>
+      <c r="G82">
+        <v>0.011</v>
+      </c>
+      <c r="H82">
+        <v>25</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.52</v>
+      </c>
+      <c r="K82">
+        <v>0.618</v>
+      </c>
+      <c r="L82">
+        <v>0.902</v>
+      </c>
+      <c r="M82">
+        <v>5.320464</v>
+      </c>
+      <c r="N82">
+        <v>-4.418464</v>
+      </c>
+      <c r="O82">
+        <v>-0.7069542400000002</v>
+      </c>
+      <c r="P82">
+        <v>-3.71150976</v>
+      </c>
+      <c r="Q82">
+        <v>-3.09350976</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3030413459286413</v>
+      </c>
+      <c r="T82">
+        <v>2.721980178905043</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02712545371982595</v>
+      </c>
+      <c r="W82">
+        <v>0.2323224416517056</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1695340857489122</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2484662225070927</v>
+      </c>
+      <c r="C83">
+        <v>-15.08473547829209</v>
+      </c>
+      <c r="D83">
+        <v>7.462764521707917</v>
+      </c>
+      <c r="E83">
+        <v>19.7085</v>
+      </c>
+      <c r="F83">
+        <v>22.5585</v>
+      </c>
+      <c r="G83">
+        <v>0.011</v>
+      </c>
+      <c r="H83">
+        <v>25</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.52</v>
+      </c>
+      <c r="K83">
+        <v>0.618</v>
+      </c>
+      <c r="L83">
+        <v>0.902</v>
+      </c>
+      <c r="M83">
+        <v>5.386969800000001</v>
+      </c>
+      <c r="N83">
+        <v>-4.484969800000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.7175951680000002</v>
+      </c>
+      <c r="P83">
+        <v>-3.767374632000001</v>
+      </c>
+      <c r="Q83">
+        <v>-3.149374632000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3169487851880435</v>
+      </c>
+      <c r="T83">
+        <v>2.865242293584256</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02679057157513673</v>
+      </c>
+      <c r="W83">
+        <v>0.2324024115078573</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1674410723446046</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2504662225070927</v>
+      </c>
+      <c r="C84">
+        <v>-15.43374993670037</v>
+      </c>
+      <c r="D84">
+        <v>7.392250063299628</v>
+      </c>
+      <c r="E84">
+        <v>19.987</v>
+      </c>
+      <c r="F84">
+        <v>22.837</v>
+      </c>
+      <c r="G84">
+        <v>0.011</v>
+      </c>
+      <c r="H84">
+        <v>25</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.52</v>
+      </c>
+      <c r="K84">
+        <v>0.618</v>
+      </c>
+      <c r="L84">
+        <v>0.902</v>
+      </c>
+      <c r="M84">
+        <v>5.453475600000001</v>
+      </c>
+      <c r="N84">
+        <v>-4.551475600000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.7282360960000003</v>
+      </c>
+      <c r="P84">
+        <v>-3.823239504</v>
+      </c>
+      <c r="Q84">
+        <v>-3.205239504000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3324014954762682</v>
+      </c>
+      <c r="T84">
+        <v>3.024422421005604</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02646385728763507</v>
+      </c>
+      <c r="W84">
+        <v>0.2324804308797127</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1653991080477192</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2524662225070927</v>
+      </c>
+      <c r="C85">
+        <v>-15.78144430889979</v>
+      </c>
+      <c r="D85">
+        <v>7.323055691100212</v>
+      </c>
+      <c r="E85">
+        <v>20.2655</v>
+      </c>
+      <c r="F85">
+        <v>23.1155</v>
+      </c>
+      <c r="G85">
+        <v>0.011</v>
+      </c>
+      <c r="H85">
+        <v>25</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.52</v>
+      </c>
+      <c r="K85">
+        <v>0.618</v>
+      </c>
+      <c r="L85">
+        <v>0.902</v>
+      </c>
+      <c r="M85">
+        <v>5.519981400000002</v>
+      </c>
+      <c r="N85">
+        <v>-4.617981400000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.7388770240000003</v>
+      </c>
+      <c r="P85">
+        <v>-3.879104376000001</v>
+      </c>
+      <c r="Q85">
+        <v>-3.261104376000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3496721716807546</v>
+      </c>
+      <c r="T85">
+        <v>3.202329622241228</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02614501563356717</v>
+      </c>
+      <c r="W85">
+        <v>0.2325565702667042</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1634063477097948</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2544662225070927</v>
+      </c>
+      <c r="C86">
+        <v>-16.12785532070285</v>
+      </c>
+      <c r="D86">
+        <v>7.25514467929715</v>
+      </c>
+      <c r="E86">
+        <v>20.544</v>
+      </c>
+      <c r="F86">
+        <v>23.394</v>
+      </c>
+      <c r="G86">
+        <v>0.011</v>
+      </c>
+      <c r="H86">
+        <v>25</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.52</v>
+      </c>
+      <c r="K86">
+        <v>0.618</v>
+      </c>
+      <c r="L86">
+        <v>0.902</v>
+      </c>
+      <c r="M86">
+        <v>5.586487200000001</v>
+      </c>
+      <c r="N86">
+        <v>-4.6844872</v>
+      </c>
+      <c r="O86">
+        <v>-0.7495179520000003</v>
+      </c>
+      <c r="P86">
+        <v>-3.934969248</v>
+      </c>
+      <c r="Q86">
+        <v>-3.316969248</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3691016824108015</v>
+      </c>
+      <c r="T86">
+        <v>3.402475223631303</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02583376544745328</v>
+      </c>
+      <c r="W86">
+        <v>0.2326308968111482</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.161461034046583</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2564662225070927</v>
+      </c>
+      <c r="C87">
+        <v>-16.47301834811915</v>
+      </c>
+      <c r="D87">
+        <v>7.188481651880843</v>
+      </c>
+      <c r="E87">
+        <v>20.8225</v>
+      </c>
+      <c r="F87">
+        <v>23.6725</v>
+      </c>
+      <c r="G87">
+        <v>0.011</v>
+      </c>
+      <c r="H87">
+        <v>25</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.52</v>
+      </c>
+      <c r="K87">
+        <v>0.618</v>
+      </c>
+      <c r="L87">
+        <v>0.902</v>
+      </c>
+      <c r="M87">
+        <v>5.652993</v>
+      </c>
+      <c r="N87">
+        <v>-4.750993</v>
+      </c>
+      <c r="O87">
+        <v>-0.7601588800000002</v>
+      </c>
+      <c r="P87">
+        <v>-3.99083412</v>
+      </c>
+      <c r="Q87">
+        <v>-3.37283412</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3911217945715217</v>
+      </c>
+      <c r="T87">
+        <v>3.629306905206723</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0255298387951303</v>
+      </c>
+      <c r="W87">
+        <v>0.2327034744957229</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1595614924695644</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2584662225070927</v>
+      </c>
+      <c r="C88">
+        <v>-16.81696747880331</v>
+      </c>
+      <c r="D88">
+        <v>7.123032521196688</v>
+      </c>
+      <c r="E88">
+        <v>21.101</v>
+      </c>
+      <c r="F88">
+        <v>23.951</v>
+      </c>
+      <c r="G88">
+        <v>0.011</v>
+      </c>
+      <c r="H88">
+        <v>25</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.52</v>
+      </c>
+      <c r="K88">
+        <v>0.618</v>
+      </c>
+      <c r="L88">
+        <v>0.902</v>
+      </c>
+      <c r="M88">
+        <v>5.7194988</v>
+      </c>
+      <c r="N88">
+        <v>-4.8174988</v>
+      </c>
+      <c r="O88">
+        <v>-0.7707998080000001</v>
+      </c>
+      <c r="P88">
+        <v>-4.046698992</v>
+      </c>
+      <c r="Q88">
+        <v>-3.428698992</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4162876370409161</v>
+      </c>
+      <c r="T88">
+        <v>3.888543112721489</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02523298020448925</v>
+      </c>
+      <c r="W88">
+        <v>0.232774364327168</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1577061262780578</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2604662225070927</v>
+      </c>
+      <c r="C89">
+        <v>-17.15973557017632</v>
+      </c>
+      <c r="D89">
+        <v>7.058764429823687</v>
+      </c>
+      <c r="E89">
+        <v>21.3795</v>
+      </c>
+      <c r="F89">
+        <v>24.2295</v>
+      </c>
+      <c r="G89">
+        <v>0.011</v>
+      </c>
+      <c r="H89">
+        <v>25</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.52</v>
+      </c>
+      <c r="K89">
+        <v>0.618</v>
+      </c>
+      <c r="L89">
+        <v>0.902</v>
+      </c>
+      <c r="M89">
+        <v>5.786004600000001</v>
+      </c>
+      <c r="N89">
+        <v>-4.884004600000001</v>
+      </c>
+      <c r="O89">
+        <v>-0.7814407360000003</v>
+      </c>
+      <c r="P89">
+        <v>-4.102563864</v>
+      </c>
+      <c r="Q89">
+        <v>-3.484563864000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.445325147582525</v>
+      </c>
+      <c r="T89">
+        <v>4.187661813700065</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02494294594926523</v>
+      </c>
+      <c r="W89">
+        <v>0.2328436245073155</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1558934121829078</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2624662225070927</v>
+      </c>
+      <c r="C90">
+        <v>-17.50135430442865</v>
+      </c>
+      <c r="D90">
+        <v>6.995645695571358</v>
+      </c>
+      <c r="E90">
+        <v>21.658</v>
+      </c>
+      <c r="F90">
+        <v>24.508</v>
+      </c>
+      <c r="G90">
+        <v>0.011</v>
+      </c>
+      <c r="H90">
+        <v>25</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.52</v>
+      </c>
+      <c r="K90">
+        <v>0.618</v>
+      </c>
+      <c r="L90">
+        <v>0.902</v>
+      </c>
+      <c r="M90">
+        <v>5.852510400000001</v>
+      </c>
+      <c r="N90">
+        <v>-4.950510400000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.7920816640000002</v>
+      </c>
+      <c r="P90">
+        <v>-4.158428736</v>
+      </c>
+      <c r="Q90">
+        <v>-3.540428736</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4792022432144022</v>
+      </c>
+      <c r="T90">
+        <v>4.536633631508405</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02465950338165995</v>
+      </c>
+      <c r="W90">
+        <v>0.2329113105924596</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1541218961353746</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2644662225070927</v>
+      </c>
+      <c r="C91">
+        <v>-17.84185424059854</v>
+      </c>
+      <c r="D91">
+        <v>6.933645759401457</v>
+      </c>
+      <c r="E91">
+        <v>21.9365</v>
+      </c>
+      <c r="F91">
+        <v>24.7865</v>
+      </c>
+      <c r="G91">
+        <v>0.011</v>
+      </c>
+      <c r="H91">
+        <v>25</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.52</v>
+      </c>
+      <c r="K91">
+        <v>0.618</v>
+      </c>
+      <c r="L91">
+        <v>0.902</v>
+      </c>
+      <c r="M91">
+        <v>5.919016200000001</v>
+      </c>
+      <c r="N91">
+        <v>-5.0170162</v>
+      </c>
+      <c r="O91">
+        <v>-0.8027225920000002</v>
+      </c>
+      <c r="P91">
+        <v>-4.214293608</v>
+      </c>
+      <c r="Q91">
+        <v>-3.596293608</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.519238810779348</v>
+      </c>
+      <c r="T91">
+        <v>4.949054870736442</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0243824303099559</v>
+      </c>
+      <c r="W91">
+        <v>0.2329774756419825</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1523901894372244</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2664662225070927</v>
+      </c>
+      <c r="C92">
+        <v>-18.18126486390531</v>
+      </c>
+      <c r="D92">
+        <v>6.872735136094694</v>
+      </c>
+      <c r="E92">
+        <v>22.215</v>
+      </c>
+      <c r="F92">
+        <v>25.065</v>
+      </c>
+      <c r="G92">
+        <v>0.011</v>
+      </c>
+      <c r="H92">
+        <v>25</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.52</v>
+      </c>
+      <c r="K92">
+        <v>0.618</v>
+      </c>
+      <c r="L92">
+        <v>0.902</v>
+      </c>
+      <c r="M92">
+        <v>5.985522</v>
+      </c>
+      <c r="N92">
+        <v>-5.083522</v>
+      </c>
+      <c r="O92">
+        <v>-0.8133635200000002</v>
+      </c>
+      <c r="P92">
+        <v>-4.27015848</v>
+      </c>
+      <c r="Q92">
+        <v>-3.65215848</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5672826918572826</v>
+      </c>
+      <c r="T92">
+        <v>5.443960357810086</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02411151441762306</v>
+      </c>
+      <c r="W92">
+        <v>0.2330421703570716</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1506969651101441</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2684662225070927</v>
+      </c>
+      <c r="C93">
+        <v>-18.51961463250489</v>
+      </c>
+      <c r="D93">
+        <v>6.812885367495115</v>
+      </c>
+      <c r="E93">
+        <v>22.4935</v>
+      </c>
+      <c r="F93">
+        <v>25.3435</v>
+      </c>
+      <c r="G93">
+        <v>0.011</v>
+      </c>
+      <c r="H93">
+        <v>25</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.52</v>
+      </c>
+      <c r="K93">
+        <v>0.618</v>
+      </c>
+      <c r="L93">
+        <v>0.902</v>
+      </c>
+      <c r="M93">
+        <v>6.052027800000001</v>
+      </c>
+      <c r="N93">
+        <v>-5.150027800000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.8240044480000003</v>
+      </c>
+      <c r="P93">
+        <v>-4.326023352000001</v>
+      </c>
+      <c r="Q93">
+        <v>-3.708023352000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6260029909525364</v>
+      </c>
+      <c r="T93">
+        <v>6.048844842011208</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0238465527207261</v>
+      </c>
+      <c r="W93">
+        <v>0.2331054432102906</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1490409545045381</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2704662225070927</v>
+      </c>
+      <c r="C94">
+        <v>-18.85693102182368</v>
+      </c>
+      <c r="D94">
+        <v>6.754068978176325</v>
+      </c>
+      <c r="E94">
+        <v>22.772</v>
+      </c>
+      <c r="F94">
+        <v>25.622</v>
+      </c>
+      <c r="G94">
+        <v>0.011</v>
+      </c>
+      <c r="H94">
+        <v>25</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.52</v>
+      </c>
+      <c r="K94">
+        <v>0.618</v>
+      </c>
+      <c r="L94">
+        <v>0.902</v>
+      </c>
+      <c r="M94">
+        <v>6.118533600000001</v>
+      </c>
+      <c r="N94">
+        <v>-5.216533600000001</v>
+      </c>
+      <c r="O94">
+        <v>-0.8346453760000003</v>
+      </c>
+      <c r="P94">
+        <v>-4.381888224000001</v>
+      </c>
+      <c r="Q94">
+        <v>-3.763888224000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6994033648216036</v>
+      </c>
+      <c r="T94">
+        <v>6.804950447262611</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02358735106071821</v>
+      </c>
+      <c r="W94">
+        <v>0.2331673405667005</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1474209441294888</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2724662225070927</v>
+      </c>
+      <c r="C95">
+        <v>-19.19324056661547</v>
+      </c>
+      <c r="D95">
+        <v>6.696259433384534</v>
+      </c>
+      <c r="E95">
+        <v>23.0505</v>
+      </c>
+      <c r="F95">
+        <v>25.9005</v>
+      </c>
+      <c r="G95">
+        <v>0.011</v>
+      </c>
+      <c r="H95">
+        <v>25</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.52</v>
+      </c>
+      <c r="K95">
+        <v>0.618</v>
+      </c>
+      <c r="L95">
+        <v>0.902</v>
+      </c>
+      <c r="M95">
+        <v>6.185039400000001</v>
+      </c>
+      <c r="N95">
+        <v>-5.283039400000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.8452863040000003</v>
+      </c>
+      <c r="P95">
+        <v>-4.437753096000001</v>
+      </c>
+      <c r="Q95">
+        <v>-3.819753096000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7937752740818329</v>
+      </c>
+      <c r="T95">
+        <v>7.777086225442985</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0233337236299578</v>
+      </c>
+      <c r="W95">
+        <v>0.2332279067971661</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1458357726872362</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2744662225070927</v>
+      </c>
+      <c r="C96">
+        <v>-19.52856890087693</v>
+      </c>
+      <c r="D96">
+        <v>6.639431099123072</v>
+      </c>
+      <c r="E96">
+        <v>23.329</v>
+      </c>
+      <c r="F96">
+        <v>26.179</v>
+      </c>
+      <c r="G96">
+        <v>0.011</v>
+      </c>
+      <c r="H96">
+        <v>25</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.52</v>
+      </c>
+      <c r="K96">
+        <v>0.618</v>
+      </c>
+      <c r="L96">
+        <v>0.902</v>
+      </c>
+      <c r="M96">
+        <v>6.251545200000001</v>
+      </c>
+      <c r="N96">
+        <v>-5.349545200000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.8559272320000002</v>
+      </c>
+      <c r="P96">
+        <v>-4.493617968000001</v>
+      </c>
+      <c r="Q96">
+        <v>-3.875617968000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9196044864288051</v>
+      </c>
+      <c r="T96">
+        <v>9.073267263016817</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02308549252751144</v>
+      </c>
+      <c r="W96">
+        <v>0.2332871843844303</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1442843282969465</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2764662225070927</v>
+      </c>
+      <c r="C97">
+        <v>-19.86294079574769</v>
+      </c>
+      <c r="D97">
+        <v>6.583559204252316</v>
+      </c>
+      <c r="E97">
+        <v>23.6075</v>
+      </c>
+      <c r="F97">
+        <v>26.4575</v>
+      </c>
+      <c r="G97">
+        <v>0.011</v>
+      </c>
+      <c r="H97">
+        <v>25</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.52</v>
+      </c>
+      <c r="K97">
+        <v>0.618</v>
+      </c>
+      <c r="L97">
+        <v>0.902</v>
+      </c>
+      <c r="M97">
+        <v>6.318051000000001</v>
+      </c>
+      <c r="N97">
+        <v>-5.416051000000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.8665681600000004</v>
+      </c>
+      <c r="P97">
+        <v>-4.549482840000001</v>
+      </c>
+      <c r="Q97">
+        <v>-3.931482840000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.095765383714567</v>
+      </c>
+      <c r="T97">
+        <v>10.88792071562019</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02284248734301132</v>
+      </c>
+      <c r="W97">
+        <v>0.2333452140224889</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1427655458938207</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2784662225070927</v>
+      </c>
+      <c r="C98">
+        <v>-20.19638019551277</v>
+      </c>
+      <c r="D98">
+        <v>6.528619804487234</v>
+      </c>
+      <c r="E98">
+        <v>23.886</v>
+      </c>
+      <c r="F98">
+        <v>26.736</v>
+      </c>
+      <c r="G98">
+        <v>0.011</v>
+      </c>
+      <c r="H98">
+        <v>25</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.52</v>
+      </c>
+      <c r="K98">
+        <v>0.618</v>
+      </c>
+      <c r="L98">
+        <v>0.902</v>
+      </c>
+      <c r="M98">
+        <v>6.3845568</v>
+      </c>
+      <c r="N98">
+        <v>-5.4825568</v>
+      </c>
+      <c r="O98">
+        <v>-0.8772090880000002</v>
+      </c>
+      <c r="P98">
+        <v>-4.605347712</v>
+      </c>
+      <c r="Q98">
+        <v>-3.987347712</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.360006729643205</v>
+      </c>
+      <c r="T98">
+        <v>13.6099008945252</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02260454476652162</v>
+      </c>
+      <c r="W98">
+        <v>0.2334020347097547</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1412784047907601</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2804662225070927</v>
+      </c>
+      <c r="C99">
+        <v>-20.52891025181735</v>
+      </c>
+      <c r="D99">
+        <v>6.474589748182649</v>
+      </c>
+      <c r="E99">
+        <v>24.1645</v>
+      </c>
+      <c r="F99">
+        <v>27.0145</v>
+      </c>
+      <c r="G99">
+        <v>0.011</v>
+      </c>
+      <c r="H99">
+        <v>25</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.52</v>
+      </c>
+      <c r="K99">
+        <v>0.618</v>
+      </c>
+      <c r="L99">
+        <v>0.902</v>
+      </c>
+      <c r="M99">
+        <v>6.451062600000001</v>
+      </c>
+      <c r="N99">
+        <v>-5.549062600000001</v>
+      </c>
+      <c r="O99">
+        <v>-0.8878500160000004</v>
+      </c>
+      <c r="P99">
+        <v>-4.661212584</v>
+      </c>
+      <c r="Q99">
+        <v>-4.043212584</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.800408972857607</v>
+      </c>
+      <c r="T99">
+        <v>18.1465345260336</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02237150822253686</v>
+      </c>
+      <c r="W99">
+        <v>0.2334576838364582</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1398219263908553</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2824662225070927</v>
+      </c>
+      <c r="C100">
+        <v>-20.86055335619649</v>
+      </c>
+      <c r="D100">
+        <v>6.421446643803509</v>
+      </c>
+      <c r="E100">
+        <v>24.443</v>
+      </c>
+      <c r="F100">
+        <v>27.293</v>
+      </c>
+      <c r="G100">
+        <v>0.011</v>
+      </c>
+      <c r="H100">
+        <v>25</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.52</v>
+      </c>
+      <c r="K100">
+        <v>0.618</v>
+      </c>
+      <c r="L100">
+        <v>0.902</v>
+      </c>
+      <c r="M100">
+        <v>6.5175684</v>
+      </c>
+      <c r="N100">
+        <v>-5.6155684</v>
+      </c>
+      <c r="O100">
+        <v>-0.8984909440000002</v>
+      </c>
+      <c r="P100">
+        <v>-4.717077456</v>
+      </c>
+      <c r="Q100">
+        <v>-4.099077456</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.681213459286411</v>
+      </c>
+      <c r="T100">
+        <v>27.2198017890504</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02214322752638853</v>
+      </c>
+      <c r="W100">
+        <v>0.2335121972666984</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1383951720399282</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2844662225070927</v>
+      </c>
+      <c r="C101">
+        <v>-21.19133117101589</v>
+      </c>
+      <c r="D101">
+        <v>6.369168828984109</v>
+      </c>
+      <c r="E101">
+        <v>24.7215</v>
+      </c>
+      <c r="F101">
+        <v>27.5715</v>
+      </c>
+      <c r="G101">
+        <v>0.011</v>
+      </c>
+      <c r="H101">
+        <v>25</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.52</v>
+      </c>
+      <c r="K101">
+        <v>0.618</v>
+      </c>
+      <c r="L101">
+        <v>0.902</v>
+      </c>
+      <c r="M101">
+        <v>6.584074200000001</v>
+      </c>
+      <c r="N101">
+        <v>-5.682074200000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.9091318720000002</v>
+      </c>
+      <c r="P101">
+        <v>-4.772942328</v>
+      </c>
+      <c r="Q101">
+        <v>-4.154942328</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.323626918572821</v>
+      </c>
+      <c r="T101">
+        <v>54.43960357810081</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02191955856147551</v>
+      </c>
+      <c r="W101">
+        <v>0.2335656094155197</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1369972410092219</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
